--- a/Output/extracted_links.xlsx
+++ b/Output/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,300 +443,6336 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>State orders closure of 258 pvt hosps over violations</t>
+          <t>मंदिरात आरती अन् कार्यकर्त्यांसोबत चहा-सामोसे! नेत्यानं वाढदिवस कसा साजरा करावा,याचे अनुकरणीय उदाहरण</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-closure-of-258-pvt-hosps-over-violations-101752780027844.html</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/cm-devendra-fadnavis-today-birthday-political-journey-maharashtra-bjp-chief-minister-devendra-fadnavis-bjp-leadership-maharashtra-cm-profile-mm76</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maha: Pending honorarium of ASHA volunteers process begins</t>
+          <t>तेव्हा कुठे होता? 'देवा भाऊं'साठी बर्थडे व्हिडिओ शेअर करून फसले मराठी कलाकार, नेटकऱ्यांनी केलं ट्रोल</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-pending-honorarium-of-asha-volunteers-process-begins-988900</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/marathi-celebrities-troll-for-share-devendra-fadnavis-birthday-video/articleshow/122850047.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
+          <t>CM Devendra Fadnavis यांच्या वाढदिवसाच्या निमित्ताने झालेल्या महारक्तदान शिबिरांची एशिया बुक ऑफ रेकॉर्डमध्ये नोंद</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
+          <t>https://www.marathi.hindusthanpost.com/social/cm-devendra-fadnavis-mass-blood-donation-camp/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maha Health Minister urges Mandaviya to revise income eligibility limit for ESIS beneficiaries</t>
+          <t>CM Devendra Fadnavis: मुख्यमंत्री देवेंद्र फडणवीस यांचा वाढदिवस सामाजिक उपक्रमाने साजरा! - देशोन्नती</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/health/maha-health-minister-urges-mandaviya-to-revise-income-eligibility-limit-for-esis-beneficiaries</t>
+          <t>https://deshonnati.com/cm-devendra-fadnavisbirthday-celebrated-social-event/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Centre to revise CGHS rates soon, union minister assures</t>
+          <t>अमृता फडणवीसांकडून देवेंद्र फडणवीसांना खास शुभेच्छा, फॅमिली फोटो शेअर करत बोलून दाखवली एक इच्छा!</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
+          <t>https://news18marathi.com/maharashtra/amrita-fadnavis-sends-special-wishes-to-devendra-fadnavis-shares-family-photos-latest-news-1440858.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
+          <t>६३ विविध सामाजिक, धार्मिक, आरोग्यवर्धक कार्यक्रमांतून मुख्यमंत्री देवेंद्र फडणवीस यांचा वाढदिवस साजरा</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
+          <t>https://chandablast.com/?p=46979</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>सरकारी दवाख्यान्यात बोगस औषध, शेल कंपन्यांकडून बोगस औषध पुरवठा</t>
+          <t>प्रिय मुख्यमंत्री... आम्ही शपथ घेतो की ...! देवेंद्र फडणवीस शिकलेल्या शाळेत अनोख्या पद्धतीने वाढदिवस साजरा</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-fake-medicine-scam-exposed-government-hospitals-pharma-racket-om0906</t>
+          <t>https://ratnagirikhabardar.com/news/69056/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ईएसआय रुग्णालयासाठी लवकरच नव्या सुविधा</t>
+          <t>मुख्यमंत्री फडणवीस यांच्या वाढदिवसानिमित्त दक्षिण जिल्ह्यातून ९०० रक्त पिशव्यांचे संकलन</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/new-facilities-soon-for-esi-hospital-health-minister-abitkar-assures-mla-seema-hire/</t>
+          <t>https://ahmednagarlive24.com/maharashtra/900-blood-bags-collected-from-south-district-on-the-occasion-of-chief-minister-fadnavis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>संगमनेरमध्ये महिलांसाठी स्वतंत्र रुग्णालय सुरू होणार, सार्वजनिक आरोग्यमंत्री प्रकाश अबिटकर यांची बैठकीत माहिती</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस यांच्या वाढदिवसानिमित्त भाजपाच्यावतीने महारक्तदान शिबिर उत्साहात संपन्न</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/ahilyanagar-news/a-separate-hospital-for-women-will-be-opened-in-sangamner-public-health-minister-prakash-abitkar-informed-in-a-meeting/</t>
+          <t>https://livemarathi.in/bjp-conducts-grand-blood-donation-camp-on-the-occasion-of-chief-minister-devendra-fadnavis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
+          <t>भाजपचा नवा विक्रम! महारक्तदान संकल्पाद्वारे विक्रमी रक्तदान; एशिया बुक ऑफ रेकॉर्ड्समध्ये नोंद</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister/ar-AA1IKKwi</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/bjp-blood-donation-asia-book-of-records.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>विधानसभा प्रश्नोत्तरे</t>
+          <t>Loni Kalbhor News: मुख्यमंत्री देवेंद्र फडणवीस आणि उपमुख्यमंत्री अजित पवार यांच्या वाढदिवसानिमित्त लोणी काळभोरमध्ये विविध समाजोपयोगी उपक्रमांचे आयोजन</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172682/</t>
+          <t>https://puneprimenews.com/pune/loni-kalbhor-news-a-series-of-social-service-activities-will-be-held-in-loni-kalbhor-on-the-occasion-of-the-birthdays-of-chief-minister-devendra-fadnavis-and-deputy-chief-minister-ajit-pawar/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>महाराष्ट्र सुश्रुषागृह कायद्याचे उल्लंघन करणाऱ्या ३३४ रुग्णालयांना टाळे</t>
+          <t>फडणवीसांचे कौतुक, खरगेंसाठी Happy Birthday, शरद पवारांकडून अजितदादांसाठी स्पेशल काय?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-closes-334-hospitals-violating-nursing-home-act-mumbai-news-amy-95-5236381/</t>
+          <t>https://news18marathi.com/maharashtra/ncp-sharad-pawar-not-wish-to-ajit-pawar-on-his-birthday-1441198.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shaktipeeth: सतेज पाटील सुट्टी देईनात, महाविकास आघाडी इर्षेला पेटली, मुख्यमंत्र्यांच्या 'ड्रीम प्रोजेक्ट'वर भाजपचं तोंड बंद!</t>
+          <t>श्री. देवेंद्र फडणवीस साहेबांच्या वाढदिवसानिमित्त आकुर्डी हॉस्पिटलमध्ये फळवाटप कार्यक्रम संपन्न</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/satej-patil-mva-attack-on-shaktipith-highway-fadnavis-dream-project-bjp-silent-dk88-rg93</t>
+          <t>https://vsrsnews.com/pune-news/fruit-distribution-program-held-at-akurdi-hospital-on-the-occasion-of-shri-devendra-fadnavis-sahebs-birthday/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
+          <t>Maharashtra Live News Update : कानात हेडफोन घालून रूळ ओलांडताना महिलेचा मृत्यू</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/shahu-maharaj-jayanti-%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%9C-%E0%A4%B0-%E0%A4%9C%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%B6-%E0%A4%B9%E0%A5%82-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%9A-%E0%A4%86%E0%A4%9C-%E0%A4%B8-%E0%A4%B9%E0%A4%B3/ar-AA1HqMYn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-22th-july-2025-parliament-monsoon-session-pm-modi-rahul-gandhi-maharashtra-politics-eknath-shinde-uddhav-thackeray-devendra-fadnavis-ajit-pawar-birthday-manikrao-kokate-mumbai-thane-nagpur-pune-nashik-weather-forecast-rain-update-rains-live-news-today-pune-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>गर्भाशयाच्या कॅन्सरची लस मोफत मिळणार!</t>
+          <t>मंत्री नितेश राणेंकडून मुख्यमंत्री सहायता निधीत १० लाख रुपये जमा</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://breakingmaharashtra.in/?p=37939</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/chief-minister-devendra-fadnavis-nitesh-rane-cheque.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>विशाळगड हिंसाचार : पडकी घरं, ठप्प व्यवहार ते कोर्टाच्या फेऱ्या; वर्षभरानंतर काय स्थिती? - ग्राऊंड रिपोर्ट</t>
+          <t>राज्यात विक्रमी १०२ रोजगार मेळावे, ५७ हजार नोंदणी, २७ हजार युवकांना एकाच दिवशी रोजगार</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/articles/cwyx2djjjyxo</t>
+          <t>https://chandablast.com/?p=47022</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
+          <t>CM Devendra Fadnavis यांच्या आवाहनाला मोठा प्रतिसाद; मुंबई बँक-मजूर फेडरेशनकडून ११.७३ लाखांचा निधी सुपूर्द!</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1286583</t>
+          <t>https://www.marathi.hindusthanpost.com/social/huge-response-to-cm-devendra-fadnavis-appeal-mumbai-bank-labor-federation-hands-over-funds-of-rs-11-73-lakh/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maha: Pending honorarium of ASHA volunteers process begins</t>
+          <t>‘क्राऊड फंडिंग’च्या माध्यमातून मुख्यमंत्री सहाय्यता निधी मिळवणार… मुख्यमंत्री सहाय्यता निधीचे महत्त्वाचे पाऊल</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/maha-pending-honorarium-of-asha-volunteers-process-begins/</t>
+          <t>https://www.loksatta.com/mumbai/first-time-in-state-cm-relief-fund-cell-to-assistance-more-patients-via-crowdfunding-and-tripartite-agreements-mumbai-print-news-sud-02-5246180/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maha: Pending honorarium of ASHA volunteers process begins</t>
+          <t>मुख्यमंत्री सहाय्यता निधी व धर्मादाय रुग्णालय मदत कक्ष – गरजूंसाठी दिलासा देणारा उपक्रम</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maha-pending-honorarium-asha-volunteers-process-begins-430153</t>
+          <t>https://mahasamvad.in/173131/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maha govt launches ‘know your doctor' system to curb bogus doctor menace</t>
+          <t>Krishi Samruddhi Scheme: फडणवीस-अजित पवारांचे शेतकऱ्यांना मोठे गिफ्ट, 25,000 कोटींची आणली नवी कृषी समृद्धी योजना Devendra Fadnavis govt brings new Krishi Samruddhi Scheme For Farmers with Rs 25,000 crore outlay t</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/maha-govt-launches-know-your-doctor-system-to-curb-bogus-doctor-menace/</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/devendra-fadnavis-govt-brings-new-krishi-samruddhi-scheme-for-farmers-with-rs-25000-crore-outlay-to-boost-agri-sector-84540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vidarbha becoming cancer capital, warns Datke</t>
+          <t>Devendra Fadnavis: शहरी माओवादी पुन्हा सक्रिय; कोलकाता, बेंगळुरुत अड्डे असल्याचा मुख्यमंत्र्यांचा दावा</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/vidarbha-becoming-cancer-capital-warns-datke/articleshow/122673957.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-claims-urban-maoists-active-again-in-kolkata-bengaluru-and-other-places/articleshow/122847447.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
+          <t>Maharashtra | आर्थिकदृष्ट्या दुर्बल आणि गरजूंच्या वैद्यकीय उपचारासाठी अधिक निधी उपलब्ध होणार; मुख्यमंत्री सहाय्यता निधीनं उचललं महत्त्वाचे पाऊल...</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-or-important-step-of-chief-minister-s-relief-fund-crowd-funding-and-tripartite-mou-have-paved-the-way-for/cid1753183799.htm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maha govt launches ‘know your doctor’ system to curb bogus doctor menace</t>
+          <t>-स्वरूपानंद पतसंस्थेकडून एक लाख</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/07/17/maha-govt-launches-know-your-doctor-system-to-curb-bogus-doctor-menace/</t>
+          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d11948-txt-ratnagiri-20250722124625</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maha Govt Launches 'Know Your Doctor' System To Curb Bogus Doctor Menace</t>
+          <t>मुख्यमंत्री वैद्यकीय सहाय्यता निधीमधून बुलढाण्यातील ३४८ रुग्णांना २ कोटी ८९ लाखांची मदत</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109815341/Maha-Govt-Launches-Know-Your-Doctor-System-To-Curb-Bogus-Doctor-Menace</t>
+          <t>https://mahasamvad.in/173097/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
+          <t>देवाभाऊ सेवा सप्ताहात 63 उपक्रमांची धडाकेबाज मालिका!</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
+          <t>https://news34.in/2025/07/devabhau-jan-kalyan-seva-saptah-chandrapur/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis &amp; Ajit Pawar Birthday: विश्वासाचा हात असू दे, मैत्रीचा सहवास असू दे! देवेंद्र फडणवीसांच्या वाढदिवसाला एकनाथ शिंदेंचं ट्विट</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/devendra-fadnavis-ajit-pawar-birthday-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%9A-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A5%82-%E0%A4%A6%E0%A5%87-%E0%A4%AE%E0%A5%88%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A-%E0%A4%B8%E0%A4%B9%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B8%E0%A5%82-%E0%A4%A6%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A2%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%B2-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%9F%E0%A5%8D%E0%A4%B5-%E0%A4%9F/ar-AA1J1VJ3?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>“तुमच्यावर नेहमी लोकांच्या प्रेमाचा वर्षाव व्हावा…”, देवेंद्र फडणवीस यांच्या वाढदिवसानिमित्त अमृता फडणवीसांची खास पोस्ट</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/photos/trending-gallery/5246247/amruta-fadnavis-birthday-wishes-for-cm-devendra-fadnavis-svk-05/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : वाढदिवस मुख्यमंत्र्यांचा…पवार अन् ठाकरेंकडून कौतुक पण शिंदेंच्या ट्वीटची का...</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/maharashtra-leaders-shower-uddhav-thackeray-sharad-pawar-praise-on-cm-devendra-fadnavis-birthday-eknath-shinde-tweet-1452523.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis &amp; Ajit Pawar Birthday: विश्वासाचा हात असू दे.. शिंदेंनी फडणवीस- अजित पवारांनी दिलेल्या वाढदिवसाच्या शुभेच्छांनी वेधलं लक्ष Dcm eknath shinde birthday wishes to devendra fadnavis and ajit pawa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/politics/dcm-eknath-shinde-birthday-wishes-to-devendra-fadnavis-and-ajit-pawar-on-birthday-84442</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis and Sharad Pawar: देवेंद्रांच्या कार्याची गती अफाट, ते थकत कसे नाहीत, हा प्रश्न मला पडतो; शरद पवारांकडून फडणवीसांवर कौतुकाचा वर्षाव</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-praises-cm-devendra-fadnavis-work-style-and-speed-give-birthday-wishes-1371651</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray : अनाजीपंत असा उल्लेख करणाऱ्या फडणवीसांना ठाकरेंनी म्हटले – मेहनती, हुशार अन् प्रामाणिक</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/uddhav-thackeray-called-devendra-fadnavis-hardworking-intelligent-and-honest-while-wishing-birthday-wishes-news-in-marathi/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>अरेच्चा वारेच फिरले! अचानक कौतुक सोहळा, ठाकरेंकडून फडणवीसांचे गुणगान काही थांबेना; राजकारणात होणार फेरफार? म्हणाले...</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/uddhav-thackeray-praise-cm-devendra-fadnavis-on-his-birthday-maharashtra-politics-937848.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis यांच्या वाढदिवसानिमित्त Sharad Pawar, Uddhav Thackeray यांच्याकडून शुभेच्छा</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://lokmat.news18.com/videos/video/sharad-pawar-uddhav-thackeray-wish-cm-devendra-fadnavis-on-his-birthday-1066902.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis and Uddhav Thackeray: देवेंद्र फडणवीस केंद्रात जाणार, उद्धव ठाकरेंकडून...</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/politics/devendra-fadnavis-is-an-ideal-politician-uddhav-thackeray-give-birthday-wishesh-to-cm-1451967.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>फडणवीसांच्या शाळेतील आठवणी सांगत अजित पवार म्हणाले, “हे मैत्री जपणारं नेतृत्व”; वाढदिवसानिमित्त दिल्या खास शुभेच्छा</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ajit-pawar-wishesh-devendra-fadnavis-for-birthday-with-heartfull-article-asc-95-5246816/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis Birthday News: वाढदिवस एकनंबरी,शुभेच्छा लय भारी Sharad Pawar Uddhav Thackeray</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://lokmat.news18.com/amp/videos/video/cm-devendra-fadnavis-birthday-news-happy-eighth-day-wishes-rhythm-bhari-sharad-pawar-uddhav-thackeray-1066958.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : मोठे नेते…फडणवीसांनी उद्धव ठाकरे आणि शरद पावारांचे मानले आभार</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-expresses-gratitude-to-sharad-pawar-and-uddhav-thackeray-for-birthday-wishes-1452201.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : वाढदिवशी मुख्यमंत्र्यांना गडचिरोली विकासाचा टिळा; राष्ट्रपती, पंतप्रधानांसह अनेक मान्यवरांकडून शुभेच्छा</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/cm-devendra-fadnavis-dedicated-his-birthday-today-entirely-to-the-development-of-gadchiroli/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray : फडणवीसांना राष्ट्रीय पातळीवर जबाबदारी मिळणार कारण… ठाकरेंकडून CM चं तोंडभरून...</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-praises-and-birthday-wishes-maharashtra-cm-devendra-fadnavis-1452042.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sharad Pawar : फडणवीसांना पाहून माझा पहिला कार्यकाळ आठवतो; पवारांकडून कौतुकाचा वर्षाव</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-showered-praise-on-devendra-fadnavis-while-wishing-him-on-his-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>शपथ समारोह वाली फोटो से अजित पवार ने फडणवीस को दी 'बर्थडे' की बधाई, दादा को किसने-किसने कहा जन्मदिन मुबारक, जानें</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/supriya-sule-with-yugendra-pawar-wishes-happy-birthday-to-ajit-pawar-dcm-congratulate-cm-fadnavis-with-oath-ceremony-photo-know-all/articleshow/122838448.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>"वह कभी थकते क्यों नहीं हैं?" देवेंद्र फडणवीस के बर्थडे पर बुक रिलीज की गई, शरद पवार ने CM की है जमकर प्रशंसा</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://hindi.oneindia.com/news/maharashtra/sharad-pawar-wishes-devendra-fadnavis-on-his-birthday-praised-in-book-why-does-he-never-get-tired-1344937.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>"...असे जीवन जगत राहा"; 'मिसेस मुख्यमंत्र्यां'ची देवेंद्र फडणवीसांच्या वाढदिवशी खास पोस्ट</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/maharashtra/amruta-fadnavis-special-post-wishesh-husband-cm-devendra-fadnavis-on-his-birthday-a-a747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sharad Pawar : “देवेंद्र फडणवीस यांच्या कार्याची गती अफाट, झपाटा आणि उरक..”, शरद पवारांकडून स्तुतीसुमनं; उद्धव ठाकरेंकडूनही कौतुक</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/sharad-pawar-gave-special-wishes-to-cm-devendra-fadnavis-says-he-is-incredible-leader-scj-81-5246366/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis: शहरी माओवादी पुन्हा सक्रिय; कोलकाता, बेंगळुरुत अड्डे असल्याचा मुख्यमंत्र्यांचा दावा</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE-%E0%A4%93%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B8%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A4%95-%E0%A4%A4-%E0%A4%AC%E0%A5%87%E0%A4%82%E0%A4%97%E0%A4%B3%E0%A5%81%E0%A4%B0%E0%A5%81%E0%A4%A4-%E0%A4%85%E0%A4%A1%E0%A5%8D%E0%A4%A1%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A6-%E0%A4%B5/ar-AA1J6wdn</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस यांनी सांगितला शरद पवार, उद्धव ठाकरेंच्या शुभेच्छांचा अर्थ: राज्यपालांची पाठराखण, म्हणाले- ...</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/devendra-fadnavis-rejects-political-meaning-birthday-wishes-sharad-pawar-uddhav-thackeray-ideological-opponents-not-enemies-135511645.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस थकत कसे नाहीत, त्यांच्या कामाचा वेग अफाट; शरद पवारांकडून कौतुकाचा वर्षाव</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/politics/ncp-sharad-pawar-appreciate-cm-devendra-fadnavis-birthday-political-news-937919.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bachchu Kadu: “आमचे कुणाशीही वैर नाही…”, बच्चू कडू मुख्यमंत्र्यांना असे का म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/bachchu-kadu-wished-devendra-fadnavis-by-posting-on-x-amy-95-5246266/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Devendra Fadanvis Birthday: फडणवीसांच्या कार्याची गती अफाट, शरद पवारांकडून स्तुतीसुमनं</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/sharad-pawar-and-uddhav-thackeray-praise-cm-devendra-fadnavis-marathi-news/925990</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Live Update : राज्याचे मुख्यमंत्री फडणवीस आणि उपमुख्यमंत्री अजित पवारांचा आज वाढदिवस</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-operation-sindoor-india-pakistan-tension-indian-armed-force-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-e-32/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis Birthday : फडणवीसांवर वाढदिवसानिमित्त कौतुकांचा वर्षाव, काय म्हणाले शरद पवार?</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/devendra-fadnavis-birthday-fadnavis-showered-with-praise-on-his-birthday-what-did-sharad-pawar-say/126878/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस केंद्रात जाणार? उद्धव ठाकरेंकडून वाढदिवसानिमित्त कौतुक; नेमके काय म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-uddhav-thackeray-praise-birthday-033129.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>विश्वासाचा हात असू दे….</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%B8%E0%A4%BE%E0%A4%9A%E0%A4%BE-%E0%A4%B9%E0%A4%BE%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A5%82-%E0%A4%A6%E0%A5%87/110594/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री सहायता निधीला स्वामी स्वरूपानंद पतसंस्थेकडून एक लाख</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/68932/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में बदलते सियासी समीकरण के बीच शरद पवार ने की फडणवीस की तारीफ, क्या बोले CM?</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-ncp-sharad-pawar-birthday-praise-for-devendra-fadnavis-what-did-cm-replied-201753206459847.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis Birthday | शरद पवार यांचे देवेंद्र फडणवीस यांच्यावर कौतुकाचा वर्षाव, 'Maharashtra Nayak' पुस्तकातून स्तुतीसुमने</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-devendra-fadnavis-birthday-sharad-pawar-uddhav-thackeray-and-other-leaders-praise-cm-in-maharashtra-nayak-book-highlighting-his-work-and-potential-national-role-1371656</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री फडणवीसांच्या वाढदिवसानिमित्त 1088 ठिकाणी रक्तदान, रवींद्र चव्हाणांचा ‘एशिया बुक ऑफ रेकॉर्ड्स’कड...</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/blood-donation-at-1088-places-on-the-occasion-of-cm-fadnavis-birthday-ravindra-chavan-honored-by-asia-book-of-records-1441986.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>त्यांच्या कामाचा झपाटा, उरक पाहून…पवारांनी केले फडणवीसांचे तोंडभरून कौतुक!</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/politics/sharad-pawar-praises-devendra-fadnavis-on-his-birthday-marathi-news-1452040.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : "फडणवीस हे हुशार, प्रामाणिक राजकारणी, भविष्यात...."; वाढदिवसानिमित्त उद्धव ठाकरेंकडून तोंडभरुन कौतुक</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/devendra-fadnavis-is-a-smart-honest-politician-uddhav-thackeray-praise-on-his-birthday-aau85</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray : अनाजीपंत असा उल्लेख करणाऱ्या फडणवीसांना ठाकरेंनी म्हटले – मेहनती, हुशार अन् प्रामाणिक</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/uddhav-thackeray-called-devendra-fadnavis-hardworking-intelligent-and-honest-while-wishing-birthday-wishes-news-in-marathi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस यांच्या वाढदिवशी जाहिराती व कॉफी टेबल बुकही</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/politics/despite-bjps-warning-banners-and-ads-flood-mumbai-for-devendra-fadnavis-birthday-celebrations-print-political-news-vsd-99-5249249/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Live Updates: कसारा रेल्वेस्थानकाजवळ लोकल ट्रेनवर दरड़ कोसळली</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/parliament-monsoon-session-2025-live-updates-maharashtra-politics-mumbai-pune-rain-news-crime-accident-local-headline-8921099</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Devendra Fadanvis : उद्धव ठाकरे, शरद पवारांकडून फडणवीसांना शुभेच्छा, लाड यांची प्रतिक्रिया</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-sharad-pawar-uddhav-thackeray-extend-birthday-wishes-to-devendra-fadnavis-bjp-leader-hints-at-uddhav-s-2019-regret-1371657</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis Ajit Pawar Birthday Special News: हॅपी बर्थडेची अशीही एक कहाणी...! N18V</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-ajit-pawar-birthday-special-news-another-such-story-of-happy-birthday-n18v-1066996.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Top 10 News : उद्धव ठाकरेंना धक्का दिलेल्या रवींद्र शिंदेंनी नवा इतिहासही घडवला, अजित पवारांची बारामती एकदा बघाचं... यासह वाचा राजकीय घडामोडी Top 10 News मध्ये...</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-news-22-jul-2025-maharashtra-politics-letest-marathi-news-politics-update-mahayuti-mva-bjp-uddhav-thackeray-chandrapur-bank-pune-metro-news-pune-crime-news-sushma-andhare-devendra-fadnavis-kalyan-viral-video-rohit-pawar-manikrao-kokate-ajit-pawar-sunil-tatkare-vijaya-rahatkar-raj-thackeray-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CM फडणवीसांची Monthly Salary किती? वर्षभरात पगार म्हणून त्यांना किती पैसे मिळतात?</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/birthday-special-how-much-salary-does-maharashtra-cm-devendra-fadnavis-get-monthly/926011</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fadnavis praised by rivals : शरद पवार, उद्धव ठाकरे यांची फडणवीस यांच्यावर स्तुतिसुमने</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/sharad-pawar-uddhav-thackeray-praise-devendra-fadnavis-ab96</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>झाला कौतुकाचा धनी!</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/sharad-pawar-and-uddhav-thackeray-praise-chief-minister-devendra-fadnavis-on-his-birthday.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : फडणवीस हुशार-प्रामाणिक, ठाकरेंकडून स्तुतिसुमनं; पवार म्हणतात देवेंद्रंना पाहून माझा कार्यकाळ आठवतो</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-praised-by-uddhav-thackeray-sharad-pawar-maharashtra-nayak-coffee-table-book-launch-on-birthday/articleshow/122834006.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Maharashtra Breaking News Today: जालन्यात सात वर्षाच्या विद्यार्थ्याची हत्या; आदिवासी निवासी वस्तीगृहातील घटना</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-22-july-bjp-leader-praful-lodha-honey-trap-case-monsoon-maharashtra-politics-national-international-live-update-in-marathi-925856</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>नक्षलग्रस्त गडचिरोली बनणार ‘स्टील हब’, मुख्यमंत्र्यांचा वाढदिवसाचा काय आहे संकल्प?</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/politics/cm-devendra-fadnavis-laid-foundation-of-steel-plant-worth-rs-24-000-crore-in-gadchiroli-02-688298</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस केंद्रात जाणार? उद्धव ठाकरेंकडून वाढदिवसानिमित्त कौतुक; नेमके काय म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-uddhav-thackeray-praise-birthday-033129.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CM फडणवीस के बर्थडे पर 27000 युवाओं को नौकरी का गिफ्ट, 57000 ने कराया पंजीयन</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/cm-fadnavis-birthday-27000-youth-got-job-1293493.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्र्यांच्या वाढदिवशी रामबाग मैदानात 100 झाडांची लागवड!</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://news34.in/2025/07/tree-plantation-drive-on-fadnavis-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>शरद पवारांचा फडणवीसांना महत्त्वाचा सल्ला: ‘राजकीय आखाड्याबाहेरील क्षितिजे पार करा’</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://politicalmaharashtra.in/sharad-pawars-important-advice-to-fadnavis-expand-horizons-beyond-the-political-arena-97160/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री फडणवीस यांच्या वाढदिवसानिमित्त रत्नागिरीत रक्तदान शिबिर</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/blood-donation-camp-held-in-ratnagiri-to-celebrate-cm-fadnaviss-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>भव्य रक्तदान शिबीर कुदळवाडीत उत्साहात पार पडले!</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://vsrsnews.com/pune-news/a-grand-blood-donation-camp-was-held-in-kudalwadi-with-enthusiasm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Mumbai News: देवेंद्र फडणवीस के जन्मदिन पर आयोजित रक्तदान शिविर में पहुंचे संजय उपाध्याय</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.nayasabera.com/2025/07/news-sanjay-upadhyay-reached-blood-donation-camp-organized-devendra-fadnavis-birthday.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>वाढदिवशी मुख्यमंत्र्यांना गडचिरोली विकासाचा टिळा…</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/173167/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : वाढदिवशी मुख्यमंत्र्यांना गडचिरोली विकासाचा टिळा; राष्ट्रपती, पंतप्रधानांसह अनेक मान्यवरांकडून शुभेच्छा</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/cm-devendra-fadnavis-dedicated-his-birthday-today-entirely-to-the-development-of-gadchiroli/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस अपने जन्मदिन के मौके पर पहुंचे गडचिरोली, कोनसारी स्थित स्टील प्लांट सहित विविध कामों का किया उद्घाटन</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.ucnnews.live/politics/chief-minister-devendra-fadnavis-reached-gadchiroli-on-the-occasion-of-his-birthday-inaugurated-various-works-including-the-steel-plant-located-at-konsari-1753174105310</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gadchiroli News | गडचिरोली काँग्रेसने लॉलीपॉप आणि चॉकलेट वाटून साजरा केला मुख्यमंत्री फडणवीसांचा वाढदिवस</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gadchiroli-congress-celebrates-fadnavis-birthday-with-lollipop-chocolates-ng81</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री तथा पालकमंत्री फडणवीसांच्या वाढदिवसानिमित्त जिल्हा काँग्रेसचे "लॉलीपॉप" वाटप आंदोलन</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.berartimes.com/political/213317/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : देवेंद्र फडणवीस गतिमान, अभ्यासू आणि पक्षनिष्ठ राजकारणी; ठाकरेंकडून कौतुक, शरद पवार म्हणाले - त्यांच्या कार्याची गती अफाट</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/devendra-fadnavis-thackeray-praise-sharad-pawar-278805/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>प्रिय मुख्यमंत्री... आम्ही शपथ घेतो की ...! फडणवीस शिकलेल्या शाळेत अनोखा वाढदिवस</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/nagpur/dear-chief-minister-we-swear-that-unique-birthday-at-the-school-where-fadnavis-studied-a-a877-c1000/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस यांचा वाढदिवसानिमित्त कराडमध्ये महारक्तदान अभियान</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/mega-blood-donation-drive-held-in-karad-on-devendra-fadnavis-birthday-ocd-94-5247354/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस, अजित पवार यांच्या वाढदिवसानिमित्त माणिक कोकाटे यांची कोणती योजना ?</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nashik/manikrao-kokate-announced-krishi-samriddhi-yojana-on-occasion-of-birthday-of-devendra-fadnavis-and-ajit-pawar-sud-02-5246390/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>"तुमचेच लोक तुमची माती करत आहेत, माणिकराव कोकाटे तुमचा व्हिडिओ कोणी केला?- सुषमा अंधारे यांची टीका</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-politics-sushma-andhare-alleges-mahayuti-mla-video-shoot-manikrao-kokate-rummy-video-warns-to-share-more-video-maharashtra-news-mhs25072300510</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस यांच्या वाढदिवसानिमित्त कल्याण पश्चिम विधानसभेतील 5 मंडळांतही रक्तदान शिबिराचे आयोजन ; तर कल्याण विकास फाउंडेशनतर्फे जल शुद्धीकरण - स्वच्छता अभियानाच</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/7/22/blood-donation-camps-were-organized-at-kalyan-on-the-occasion-of-cms-birthday.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray : अनाजीपंत असा उल्लेख करणाऱ्या फडणवीसांना ठाकरेंनी म्हटले – मेहनती, हुशार अन् प्रामाणिक</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/uddhav-thackeray-called-devendra-fadnavis-hardworking-intelligent-and-honest-while-wishing-birthday-wishes-news-in-marathi/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis B'day : 'तेव्हाच कळलं होतं, हा तरुण अत्यंत धडपडा' : गडकरींनी सांगितली 'फडणवीसांच्या' राजकीय एन्ट्रींची आठवण</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/vishesh/devendra-fadnavis-birthday-nitin-gadkari-political-journey-tribute-maharashtra-bjp-leadership-hn97</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस के जन्मदिन पर रक्तदान शिविर</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/blood-donation-camp-on-the-birthday-of-chief-minister-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jaykumar Gore | श्रीक्षेत्र रेवणसिद्ध मंदिरासाठी ५ कोटी ; बाणूरगड-भाळवणीसाठीही निधी देणार: जयकुमार गोरे यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/jaykumar-gore-%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B0%E0%A5%87%E0%A4%B5%E0%A4%A3%E0%A4%B8-%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AE%E0%A4%82%E0%A4%A6-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A5%AB-%E0%A4%95-%E0%A4%9F-%E0%A4%AC-%E0%A4%A3%E0%A5%82%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%AD-%E0%A4%B3%E0%A4%B5%E0%A4%A3-%E0%A4%B8-%E0%A4%A0-%E0%A4%B9-%E0%A4%A8-%E0%A4%A7-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%9C%E0%A4%AF%E0%A4%95%E0%A5%81%E0%A4%AE-%E0%A4%B0-%E0%A4%97-%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1J84AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CM देवेंद्र के जन्मदिन पर BJP का रक्तदान, एशिया बुक ऑफ वर्ल्ड रिकॉर्ड्स में दर्ज</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/bjp-blood-donation-on-cm-fadnavis-birthday-recorded-in-asia-book-of-world-records-1294540.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>55 वर्ष के हुए देवेंद्र फडणवीस– महाराष्ट्र के भविष्य को आकार देने वाले एक दूरदर्शी नेता</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.theprintlines.com/tpspecial/meri-baat/devendra-fadnavis-turns-55-a-visionary-leader-who-shaped-the-future-of-maharashtra-428416</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री फडणवीस यांच्या वाढदिवसानिमित्त आमदार रहांगडाले यांच्या पुढाकाराने रक्तदान शिबिराचे आयोजन</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.berartimes.com/vidarbha/213303/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>उद्धव ठाकरे ने देवेंद्र फडणवीस को जन्मदिन की बधाई देते की तारीफ, बावनकुले बोले- यह महाराष्ट्र की परंपरा</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.ucnnews.live/politics/uddhav-thackeray-praised-devendra-fadnavis-for-wishing-him-on-his-birthday-bawankule-said-this-is-a-tradition-of-maharashtra-1753259907799</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>विरोधकांचे हनीट्रॅप आरोप पेन ड्राईव्हच्या बाहेर येण्यास तयार नाहीत : चंद्रशेखर बावनकुळे</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-slams-opposition-leader-over-honey-trapped-case-girish-mahajan-devendra-fadnavis-maharashtra-news-mhs25072302644</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis | शरद पवारांनी असे शब्द माझ्या साठी वापरणे हा त्यांचा...: देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/devendra-fadnavis-responds-to-sharad-pawar-statement-as80</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>फडणवीस प्रामाणिक आणि हुशार, भविष्यात त्यांना केंद्रात मोठी संधी मिळण्याची शक्यता; उद्धव ठाकरेंची मुख्यमंत्र्यांवर स्तुतीसुमने</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/devendra-fadnavis-birthday-uddhav-thackeray-praise-for-maharashtra-cm-bjp-leader-girish-mahajan-coffee-table-book-marathi-news-1371658</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis | शरद पवारांनी असे शब्द माझ्या साठी वापरणे हा त्यांचा...: देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%85%E0%A4%B8%E0%A5%87-%E0%A4%B6%E0%A4%AC%E0%A5%8D%E0%A4%A6-%E0%A4%AE-%E0%A4%9D%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%B5-%E0%A4%AA%E0%A4%B0%E0%A4%A3%E0%A5%87-%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1J4ogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis Birthday : वडिलांचे संस्कार, संघाचा वारसा आणि ‘रसवंतीगृह’ ते मुख्यमंत्रिपदाचा प्रवास</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/special/devendra-fadnavis-birthday-gangadharrao-kashirao-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>एकाच दिवशी जन्मलेले दोन 'हुकमी एक्के'; महाराष्ट्राच्या राजकारणात फडणवीस-पवार यांची जुळवून घेतलेली युती!</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.nagpurtoday.in/two-aces-of-command-born-on-the-same-day-fadnavis-pawars-alliance-in-maharashtra-politics/07221715</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Nagpur News : उद्धव ठाकरेंच्या जागा घटल्यामुळे भाजप नेत्याचा संजय राऊत यांना टोला, दिला जोरदार इशारा</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://marathi.timesnownews.com/maharashtra/chandrashekhar-bawankule-slams-sanjay-raut-over-remarks-against-pm-modi-issues-strong-warning-article-152324507</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Gadchiroli News | गडचिरोली काँग्रेसने लॉलीपॉप आणि चॉकलेट वाटून साजरा केला मुख्यमंत्री फडणवीसांचा वाढदिवस</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/amp/story/maharashtra/vidarbha/gadchiroli/gadchiroli-congress-celebrates-fadnavis-birthday-with-lollipop-chocolates-ng81</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>बावनकुळे: उद्धवजींचं कौतुक राज्याच्या राजकारणाला सकारात्मक दिशा देणार</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/bawankule-welcomes-uddhav-thackerays-praise-for-fadnavis-as-positive-politics-rds-00-5248527/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray : “देवेंद्र फडणवीस प्रामाणिक राजकारणी”; उद्धव ठाकरेंकडून खास लेख लिहित कौतुक</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-is-an-honest-politician-praised-by-uddhav-thackeray-in-a-special-article-on-his-birth-day-scj-81-5246714/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>गडकरींच्या पावलावर पाऊल; बावनकुळे म्हणतात,” नोकरी मागणारे नव्हे तर..”</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-appealed-to-the-unemployed-at-the-nagpur-pandit-deendayal-upadhyay-employment-fair-mnb-82-phm-00-5247001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Maharashtra: उद्धव ठाकरे-शरद पवार गुट ने की देवेंद्र फडणवीस की तारीफ, CM बोले- 'वैचारिक विरोधी</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/on-birthday-devendra-fadnavis-launched-coffee-table-book-on-sharad-pawar-and-uddhav-thackeray-ideological-differences-2983872</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>'भविष्य में देवेंद्र फडणवीस को केंद्र में मिल सकती है बड़ी जिम्मेदारी', उद्धव</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-praises-maharashtra-cm-devendra-fadnavis-in-a-coffee-book-on-his-55th-birthday-for-his-tremendous-work-ann-2983736</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>अभीष्टचिंतनाचा अन्य अर्थ काढणे संकुचित वृत्ती – देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/dont-politicise-birthday-greetings-fadnavis-hits-back-ocd-94-5250551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis | वाढदिवशी मुख्यमंत्री फडणवीस करणार गडचिरोलीत एलएमईएलच्या स्टील प्रकल्पाचा शिलान्यास</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%B5-%E0%A4%A2%E0%A4%A6-%E0%A4%B5%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%97%E0%A4%A1%E0%A4%9A-%E0%A4%B0-%E0%A4%B2-%E0%A4%A4-%E0%A4%8F%E0%A4%B2%E0%A4%8F%E0%A4%AE%E0%A4%88%E0%A4%8F%E0%A4%B2%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%B6-%E0%A4%B2-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B8/ar-AA1IR3wo?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्याच्या वाढदिवसाला रक्तदान व वृक्ष लागवड कार्यक्रमाला उत्तम प्रतिसाद! -</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/cm-devendra-fadnavisblood-donation-plantation-cm-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस यांनी महाराष्ट्राला प्रगतीपथावर नेले – राज्यपाल सी. पी. राधाकृष्णन</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/173069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>फडणवीसांपेक्षा मिसेस CM श्रीमंत; अमृता फडणवीस यांच्या प्रत्येक लुकमध्ये दिसतो हटके अंदाज</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/lifestyle-news/fashion/birthday-special-cm-devendra-fadnavis-wife-amruta-fadnavis-classic-look/articleshow/122831682.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>विक्रमी १०२ रोजगार मेळावे घेत साजरा झाला मुख्यमंत्र्यांचा वाढदिवस - कौशल्य विकास मंत्री मंगलप्रभात लोढा यांची अभिनव संकल्पना</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/7/22/chief-ministers-birthday-celebrated-by-holding-a-record-102-job-fairs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीसांच्या कामाची गती आणि झपाटा कौतुकास्पद – शरद पवार</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/7/22/opposition-leader-sharad-pawar-and-uddhav-thackeray-speak-about-cm-on-his-birthday-.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>कृषीमंत्र्यांचा रमीचा डाव; मुख्यमंत्र्यांनी नाराजी व्यक्त केल्यानंतर कोकाटे म्हणाले…</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5245931/after-chief-minister-devendra-fadnavis-expressed-displeasure-agriculture-minister-manikrao-kokate-said/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांच्या वाढदिवसानिमित्त कांदिवली पूर्व येथे रक्तदान शिबीर</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.newsdanka.com/vishesh/blood-donation-camp-on-the-occassion-of-birthday-celebration-of-cm-devendra-fadanvis-in-kandivali/160188/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CP Radhakrishnan : मुख्यमंत्री फडणवीसांनी महाराष्ट्राला प्रगतीपथावर नेले; राज्यपालांचे प्रतिपादन</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/governor-cp-radhakrishnan-asserted-that-chief-minister-devendra-fadnavis-has-taken-maharashtra-on-the-path-of-progress/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Government Scheme: शेतीच्या विकासासाठी महाराष्ट्र सरकार करणार दरवर्षी 5000 कोटींची गुंतवणूक! नवीन योजना सुरू</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://krushimarathi.com/agriculture-government-scheme-maharashtra-government-to-invest-rs-5000-crores-annually-for-agricultural-development-new-scheme-launched/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>गढ़चिरौली जिले में विकास कार्यों की शुरुआत कर मुख्यमंत्री फडणवीस ने मनाया अपना जन्मदिन</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/7/22/cm-fadnvis-celebrate-his-birthday-with-works.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>गडचिरोली देशातील सर्वाधिक हरित जिल्हा बनविण्याचा मुख्यमंत्री देवेंद्र फडणवीस यांचा संकल्प</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/173144/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis-Sharad Pawar: "देवेंद्र फडणवीसांचा कामाचा झपाटा आणि उरक पाहिला की, मला…"; शरद पवारांकडून फडणवीसांवर कौतुकाचा वर्षाव</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/ncp-sharad-pawar-praises-cm-devendra-fadnavis-on-his-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>आधुनिक तंत्रज्ञानाच्या युगात विविध क्षेत्रातील नव्या रोजगार संधींचा तरुणांनी लाभ घ्यावा :पालकमंत्री जयकुमार रावल</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/173101/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : वाढदिवशी मुख्यमंत्र्यांना गडचिरोली विकासाचा टिळा; राष्ट्रपती, पंतप्रधानांसह अनेक मान्यवरांकडून शुभेच्छा</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/cm-devendra-fadnavis-dedicated-his-birthday-today-entirely-to-the-development-of-gadchiroli/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Employment Opportunities for Youth in Maharashtra: महाराष्ट्र में एक दिन में 27 हजार युवाओं को मिला रोजगार, 102 जगहों पर लगे मेगा जॉब फेयर</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://thecsrjournal.in/employment-opportunities-for-youth-in-maharashtra-hindi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में रोज़गार मेले के ज़रिए एक दिन में 27 हज़ार युवाओं को मिली नौकरी | Tap to know more | Inshorts</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://inshorts.com/hi/news/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7-%E0%A4%9F-%E0%A4%B0-%E0%A4%AE---%E0%A4%B0-%E0%A5%9B%E0%A4%97-%E0%A4%B0-%E0%A4%AE-%E0%A4%B2--%E0%A4%95--%E0%A5%9B%E0%A4%B0-%E0%A4%8F-%E0%A4%8F%E0%A4%95-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE---27-%E0%A4%B9%E0%A5%9B-%E0%A4%B0-%E0%A4%AF-%E0%A4%B5-%E0%A4%93--%E0%A4%95--%E0%A4%AE-%E0%A4%B2--%E0%A4%A8-%E0%A4%95%E0%A4%B0---1753268648951</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस के जन्मदिन पर भव्य रक्तदान शिविर</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/grand-blood-donation-camp-on-chief-minister-devendra-fadnavis-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>फडणवीस के जन्मदिन पर रक्तदान कर बधाई</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/congratulate-fadnavis-by-donating-blood-on-his-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PM Modi ने अजित पवार और देवेंद्र फडणवीस को जन्मदिन की दीं शुभकामनाएं</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/amp/delhi-ncr/pm-modi-wishes-ajit-pawar-and-devendra-fadnavis-on-their-birthdays-4163935</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis को Chandrashekhar Bawankule का भावुक पत्र, एक बार जरूर पढ़ना चाहिए</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.khabar24.tv/2025/07/24/chandrashekhar-bawankule-emotional-letter-to-devendra-fadnavis-must-read-once/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>प्रधानमंत्री मोदी ने फडणवीस और अजित पवार को जन्मदिन की शुभकामनाएं दीं</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A6-%E0%A4%A8%E0%A5%87-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%94%E0%A4%B0-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%95-%E0%A4%B6%E0%A5%81%E0%A4%AD%E0%A4%95-%E0%A4%AE%E0%A4%A8-%E0%A4%8F%E0%A4%82-%E0%A4%A6-%E0%A4%82/ar-AA1J4jGv</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>देश की खबरें | प्रधानमंत्री मोदी ने फडणवीस और अजित पवार को जन्मदिन की शुभकामनाएं दीं</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/agency-news/prime-minister-modi-greeted-fadnavis-and-ajit-pawar-on-his-birthday-2704460.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PM Modi ने अजित पवार और देवेंद्र फडणवीस को जन्मदिन की दीं शुभकामनाएं</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/delhi-ncr/pm-modi-wishes-ajit-pawar-and-devendra-fadnavis-on-their-birthdays-4163935</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>पूर्व नगरसेवक विजय शिंदे ने 55 देशी पौधे लगाए – Hindi e news Paper Online | Latest News Hindi</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://vsrsnews.in/pune-city/pune-former-corporator-vijay-shinde-planted-55-native-saplings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>प्रधानमंत्री मोदी ने फडणवीस और अजित पवार को जन्मदिन की शुभकामनाएं दीं</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/pm-modi-wishes-fadnavis-and-ajit-pawar-on-their-birthdays/845874/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Krishi Samruddhi Yojna: महाराष्ट्र के किसानों को बड़ी सौगात, 25000 करोड़ रुपये की नई योजना का ऐलान</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/mumbai-news/big-gift-to-farmers-of-maharashtra-new-scheme-of-rs-25000-crore-announced-19801008</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र सरकार ने कृषि क्षेत्र को बढ़ावा देने के लिए 25,000 करोड़ रुपये की योजना पेश की</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/economy/maharashtra-government-launches-rs-25000-crore-scheme-to-boost-agriculture-sector/845871/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र : सरकार ने शुरू की किसानों के लिए महत्वपूर्ण योजना, खेती के लिए 25000 करोड़ की सौगात</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/maharashtra-government-started-an-important-scheme-kisan-samridhi-yojana-for-farmers-agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>नहीं दिख रहा था हेलीपैड, शिंदे ने कहा कोशिश करो, पायलट ने कहा 'महंगा' पड़ेगा...</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/wardha/thrilling-story-of-shindes-helicopter-helicopter-did-not-land-even-after-reaching-wardha-1293718.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Nurse Nimisha Priya Case: राष्ट्रपति मुर्मू और पीएम मोदी को पत्र लिख मदद मांगेंगे भारत के ग्रैंड मुफ्ती</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/india/nurse-nimisha-priya-case-grand-mufti-of-india-will-write-a-letter-to-president-murmu-and-pm-modi-asking-for-help-2704269.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>जन्मदिन पर देवाभाऊ की हुई सराहना…फडणवीस जल्द जाएंगे दिल्ली… पवार और उद्धव ठाकरे ने दीं शुभकामनाएं</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://www.hindisaamana.com/devabhau-was-praised-on-his-birthday-fadnavis-will-soon-go-to-delhi-pawar-and-uddhav-thackeray-gave-best-wishes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>इतनी मेहनत करतें है पर थकते क्यों नहीं? शरद पवार ने बांधे फडणवीस के तारीफों के पुल</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.prabhasakshi.com/national/why-do-you-work-so-hard-but-dot-you-get-tired-sharad-pawar-praises-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>विपक्षी नेताओं की ओर से जन्मदिन पर मिली शुभकामनाओं को राजनीतिक रंग देना गलत: मुख्यमंत्री फडणवीस</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/it-is-wrong-to-give-political-colour-to-birthday-wishes-received-from-opposition-leaders-cm-fadnavis/846220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>फडणवीस में खुद की छवि देखते है शरद पवार, बोले- थकते क्यों नहीं हैं देवेंद्र</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ncp-sharad-pawar-praised-bjp-cm-devendra-fadnavis-1293822.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>पहले CM देवेंद्र फडणवीस से मिले उद्धव ठाकरे, फिर बर्थडे पर की तारीफ, अब कांग्रेस</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-devendra-fadnavis-meeting-congress-leader-arif-naseem-khan-reaction-2984268</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>विपक्षी नेताओं की ओर से जन्मदिन पर मिली शुभकामनाओं को राजनीतिक रंग देना गलत: मुख्यमंत्री फडणवीस</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/it-is-wrong-to-give-political-colour-to-birthday-wishes-received-from-opposition-leaders-cm-fadnavis/846220/?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में क्या पक रहा है? शरद पवार-उद्धव ठाकरे ने फडणवीस की तारीफ की, सीएम बोले- हम व्यक्तिगत दुश्मन नहीं - CM Fadnavis thanked Sharad Pawar and Uddhav Thackeray for their praise</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/news/national-cm-fadnavis-thanked-sharad-pawar-and-uddhav-thackeray-for-their-praise-23991634.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>'हम वैचारिक रूप से विरोधी हैं, व्यक्तिगत दुश्मन नहीं...', उद्धव ठाकरे और शरद पवार पर बोले फडणवीस</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/we-are-ideological-opponents-not-enemies-says-devendra-fadnavis-on-udhhav-thackeray-sharad-pawar-lclnt-dskc-2293760-2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CM फडणवीस के मुरीद हुए शरद पवार, कहा- उन्हें देखकर अपने दिन याद आते हैं, वो कभी नहीं थकते</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/mumbai-news/sharad-pawar-praises-maharashtra-cm-devendra-fadnavis-said-he-never-get-tired-19799092</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र: इतनी मेहनत करते हैं पर थकते क्यों नहीं? शरद पवार ने CM फडणवीस की क्यों कर दी इतनी तारीफ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/maharashtra/something-new-in-maharashtra-now-ncp-chief-sharad-pawar-praise-cm-fadnavis-so-much-2025-07-22-1151011</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>'हम वैचारिक विरोधी, दुश्मन नहीं'. शरद पवार-उद्धव की तारीफ पर बोले फडणवीस- उनके शब्द मेरे लिए अनमोल</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-fadnavis-says-uddhav-sharad-not-enemies-just-political-opponents-9430659.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis: 'हम दुश्मन नहीं हैं', महाराष्ट्र के CM देवेंद्र फडणवीस ने उद्धव ठाकरे, शरद पवार को दिया धन्यवाद, जानिए क्यों?</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-thanks-opponents-uddhav-thackeray-sharad-pawar-and-says-we-arent-enemies-know-why/articleshow/122841206.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: कभी थकते नहीं... शरद पवार ने देवेंद्र फडणवीस को बताया अद्वितीय, उद्धव ने भी खुलकर सरा...</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/amp/news/maharashtra/mumbai-sharad-pawar-uddhav-thackeray-praised-devendra-fadnavis-called-him-unique-on-book-launch-9429650.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>'वे थकते क्यों नहीं', शरद पवार ने CM देवेंद्र फडणवीस के जन्मदिन पर जमकर की तारीफ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-birthday-sharad-pawar-ncp-sp-praised-maharashtra-cm-ann-2983631</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>योगी आदित्यनाथ ने दी महाराष्ट्र के मुख्यमंत्री फडणवीस को जन्मदिन पर बधाई</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A4%A8-%E0%A4%A5-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7-%E0%A4%88/ar-AA1J2kQO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>जन्मदिन पर गड़चिरोली पहुंचे CM फडणवीस, पालकमंत्री ने जिले को दी ये सौंगात</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/garchiroli/cm-devendra-fadnavis-laid-foundation-stone-and-inaugurated-development-works-in-gadiroli-1293289.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>देश की खबरें | ठाकरे, पवार के बारे में फडणवीस ने कहा: हम वैचारिक रूप से विरोधी हैं, दुश्मन नहीं</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/agency-news/talking-about-thackeray-pawar-fadnavis-said-we-are-ideologically-opposed-not-enemies-r-2-2704734.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis Gadchiroli News: बॅर्थडेला मुख्यमंत्र्यांचा मोठा निर्धार! विकासाचा प्लॅनच सांगितला</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-gadchiroli-news-chief-minister-s-big-decision-on-birthday-development-plan-announced-1066952.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>बदल रही फिजा! ये क्‍या हुआ, उद्धव-शरद पवार अचानक क्‍यों हो गए फडणवीस के फैन?</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/explainer/uddhav-thackeray-and-sharad-pawar-praises-devendra-fadnavis-chandrashekhar-bawankule-response/2851753</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>नगर विकास पर अंकुश</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/other-cities/curbing-urban-development/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>राज्यस्तरीय कविसंमेलनाच्या अध्यक्षपदी कवी डॉ.धनराज खानोरकरांची निवड</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://chandablast.com/?p=46985</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>राजनीति में ‘U-Turn’? फडणवीस को लेकर उद्धव-पवार के बदले बोल</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://www.jubileepost.in/u-turn-in-politics-uddhav-pawars-changed-words-about-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में बदलते सियासी समीकरण के बीच शरद पवार ने की फडणवीस की तारीफ, क्या बोले CM?</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-ncp-sharad-pawar-birthday-praise-for-devendra-fadnavis-what-did-cm-replied-201753206459847.amp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>अजित पवार के बर्थडे पर अनोखी बधाई देकर अब बुरे फंसे विधानसभा सत्र में रमी खेलने वाले मंत्री, लग रहे ये आरोप</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://hindi.oneindia.com/news/maharashtra/rummy-playing-minister-manikrao-kokate-got-into-trouble-by-giving-unique-wish-on-ajit-pawar-birthday-1344851.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>रमी विवाद, किसानों को कहा भिखारी, अब बोले सरकार भिखारी, महाराष्ट्र में माणिकराव कोकाटे को क्या हुआ?</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/manikrao-kokate-refers-maharashtra-govt-beggar-triggers-new-row-after-rummy-playing-video/articleshow/122846731.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>देश की खबरें | विपक्षी नेताओं की ओर से जन्मदिन पर मिली शुभकामनाओं को राजनीतिक रंग देना गलत:</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/agency-news/it-is-wrong-to-give-political-color-to-the-best-wishes-received-by-opposition-leaders-on-birthday-chief-minister-fadnavis-r-2705676.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ठाकरे, पवार के बारे में फडणवीस ने कहा: हम वैचारिक रूप से विरोधी हैं, दुश्मन नहीं</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://www.ibc24.in/maharashtra/we-are-ideologically-opponents-not-enemies-fadnavis-on-thackeray-pawar-3174541.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>प्रधानमंत्री मोदी ने फडणवीस और अजित पवार को जन्मदिन की शुभकामनाएं दीं</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://www.ibc24.in/maharashtra/pm-modi-wishes-fadnavis-ajit-pawar-on-their-birthdays-3174489.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MHADA Konkan Lottery 2025: मुंबई से बाहर घर खरीदने का सुनहरा मौका, 5000 से ज्यादा घरों के लिए आवेदन प्रक्रिया शुरू, जानें अंतिम तारीख और एप्लीकेशन से जुड़ी अन्य डिटेल्स</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/india/information/mhada-konkan-board-lottery-2025-apply-now-for-5000-homes-know-last-date-other-details-2705181.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: शरद पवार-उद्धव ने की CM फडणवीस की तारीफ, भाजपा नेता बोले- यह राज्य की संस्कृति का हिस्सा</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/sharad-pawar-uddhav-praised-cm-fadnavis-bjp-leader-said-this-is-a-part-of-the-state-s-culture-2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: शरद पवार-उद्धव ने की CM फडणवीस की तारीफ, भाजपा नेता बोले- यह राज्य की संस्कृति का हिस्सा</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-politics-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A8%E0%A5%87-%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A4%B9-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1J72wi</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>‘शरद और उद्धव की पार्टी लगातार भाजपा के संपर्क में’, केसी त्यागी ने किया महाराष्ट्र में उलटफेर का दावा</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%94%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95%E0%A5%80-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%9F%E0%A5%80-%E0%A4%B2%E0%A4%97%E0%A4%BE/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>फडणवीस के 55वें जन्मदिन पर सहयोगियों और विरोधियों ने दी बधाई</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/allies-and-opponents-congratulated-fadnavis-on-his-55th-birthday-4164496</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>'भविष्य में देवेंद्र फडणवीस को केंद्र में मिल सकती है बड़ी जिम्मेदारी', उद्धव ठाकरे ने दी जन्मदिन की बधाई</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AD%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE-%E0%A4%B2-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9C-%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A5%87%E0%A4%A6-%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A4%A7-%E0%A4%88/ar-AA1J4SXl</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>धारणी के अस्पताल को नागपुर एम्स की सेवाएं</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/dharni-hospital-gets-services-of-aiims-nagpur/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>JDU का दावा, उद्धव और शरद CM फडणवीस के संपर्क में, बदलाव के लिए रहे तैयार</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/jdu-leader-kc-tyagi-claims-sharad-pawar-and-uddhav-thackeray-are-in-touch-with-cm-fadnavis-maharashtra-politics-1294128.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>विदर्भ में आज से मूसलाधार</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/rainfall-in-vidarbha-today/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Jagdeep Dhankhar Resigns: उपराष्ट्रपति जगदीप धनखड़ का</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://primetvindia.com/jagdeep-dhankhar-resigns-vice-president-jagdeep-dhankhars-resignation-accepted-decided-to-resign-from-the-post-citing-health-reasons/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Vijay Wadettiwar on Manikrao Kokate: विजय वडेट्टीवार ने माणिकराव कोकाटे के बयान का किया सर्मथन, बोले- महाराष्ट्र</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/india/vijay-wadettiwar-on-manikrao-kokate-vijay-wadettiwar-supported-manikrao-kokates-statement-said-the-condition-of-maharashtra-government-is-worse-2705024.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ठाकरे, पवार के बारे में फडणवीस ने कहा: हम वैचारिक रूप से विरोधी हैं, दुश्मन नहीं</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://navabharat.news/we-are-ideological-opponents-not-enemies-fadnavis-on-thackeray-pawar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sharad Pawar, Uddhav Thackeray heap praises on Fadnavis on latter's birthday</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/sharad-pawar-uddhav-thackeray-heap-praises-on-fadnavis-on-latters-birthday-3642663</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>गढ़चिरौली जिले में विकास कार्यों की शुरुआत कर मुख्यमंत्री फडणवीस ने मनाया अपना जन्मदिन</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://vocaltv.in/national/cm-fadnvis-celebrate-his-birthday-with-worksphp/cid17130059.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Mumbai News: मुख्यमंत्री के नेतृत्व में विकास की नई ऊंचाइयों की तरफ बढ़ रहा महाराष्ट्र: कृपाशंकर</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.nayasabera.com/2025/07/maharashtra-moving-towards-new-heights-development-leadership-chief-minister-kripashankar.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>गढ़चिरौली को विकास से दूर रखने के लिए ‘शहरी नक्सली’ कर रहे विदेशी धन का इस्तेमाल: फडणवीस</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://navabharat.news/urban-naxals-using-foreign-funds-to-keep-gadchiroli-away-from-development-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Record 102 Job Fairs On Maharashtra CM Devendra Fadnavis Birthday See 57,000 Registrations, 27,000 Employed</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/record-102-job-fairs-on-maharashtra-cm-devendra-fadnavis-birthday-see-57000-registrations-27000-employed-in-single-day</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CM Fadnavis’ Birthday Celebrated with Statewide Social Initiatives and Public Participation</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/cm-fadnavis-birthday-celebrated-with-statewide-social-initiatives-and-public-participation/articleshow/122844566.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Pune: Food Distribution And Book Donation Drive Held In Wanawadi To Celebrate Devendra Fadnavis’s Birthday</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/pune-food-distribution-and-book-donation-drive-held-in-wanawadi-to-celebrate-devendra-fadnaviss-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Gift to children on CM Fadnavis’ birthday: Uniforms distributed</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/gift-to-children-on-cm-fadnavis-birthday-uniforms-distributed/articleshow/122843477.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Maharashtra Government Takes Acquittal Of 2006 Mumbai Train Bombings To Supreme Court; Hearing Scheduled For Tomorrow</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-takes-acquittal-of-2006-mumbai-train-bombings-to-supreme-court-hearing-scheduled-for-tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4 Dead, Half Dozen Injured After Speeding Car Runs Over Devotees While Walking On Gwalior Highway</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/bhopal/4-dead-half-dozen-injured-after-speeding-car-runs-over-devotees-while-walking-on-gwalior-highway</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PM Modi extends birthday greetings to Maha CM Fadnavis, Deputy CM Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/en/pm-modi-extends-birthday-greetings-to-maha-cm-fadnavis-deputy-cm-ajit-pawar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi, Mallikarjun Kharge Meet J&amp;K Congress Leaders As Party Links Vice President Jagdeep Dhankhar’s</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/india/rahul-gandhi-mallikarjun-kharge-meet-jk-congress-leaders-as-party-links-vice-president-jagdeep-dhankhars-exit-to-deeper-bjp-dysfunction</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PM Modi extends birthday wishes to Fadnavis and Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/07/22/bes19-mh-modi-fadnavis.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>RTO Team’s Quick Response Saves Three After Bike Accident On Pune-Kolhapur Highway</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/rto-teams-quick-response-saves-three-after-bike-accident-on-pune-kolhapur-highway/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis Birthday News: Sharad Pawar - Uddhav Thackeray यांच्याकडून फडणवीसांचं कौतुक</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-birthday-news-sharad-pawar-uddhav-thackeray-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%95/vi-AA1J4rvR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Mumbai: 78-Year-Old Woman Duped By 2 Fake Cops On Bandras Hill Road; Gold Bangles Worth ₹1.4 Lakh Stolen,</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-78-year-old-woman-duped-by-2-fake-cops-on-bandras-hill-road-gold-bangles-worth-14-lakh-stolen-fir-filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Cabinet Approves India-UK Free Trade Agreement, PM Modi To Sign In London On July 24</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/world/cabinet-approves-india-uk-free-trade-agreement-pm-modi-to-sign-in-london-on-july-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Hamas Causes Crisis, And We Get The Blame: Israels UN Ambassador Danny Danon On Gaza</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/world/hamas-causes-crisis-and-we-get-the-blame-israels-un-ambassador-danny-danon-on-gaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Samajwadi Party Kicks Off Campaign For Panchayat Polls, Launches PDA Leaflet Drive In Villages</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/india/samajwadi-party-kicks-off-campaign-for-panchayat-polls-launches-pda-leaflet-drive-in-villages</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Mira Bhayandar News: CM Fadnavis’ birthday marked as ‘Seva Diwas’ in Mira-Bhayandar</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://www.newsband.in/article_detail/mira-bhayandar-news-cm-fadnavisbirthdaymarkedas-seva-diwas-inmira-bhayandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Wrong to give political colour to birthday wishes of Pawar, Thackeray: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/wrong-to-give-political-colour-to-birthday-wishes-of-pawar-thackeray-fadnavis-101753300048101.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांच्या वाढदिवसानिमित्तानं पुण्यात सामूहिक अथर्वशीर्ष पठण, 221 ब्रह्मवृंदांचा सहभाग</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/ganpati-atharvashirsha-pathan-in-pune-on-the-occasion-of-chief-minister-devendra-fadnavis-birthday-maharashtra-news-mhs25072202931</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sharad Pawar hails Devendra Fadnavis on his 55th Birthday</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/news/india/sharad-pawar-and-uddhav-thackeray-hails-devendra-fadnavis-on-his-55th-birthday-13308659.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Gadchiroli Will Figure Among Top 10 Districts Of Maharashtra In 5 Years: CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/gadchiroli-will-figure-among-top-10-districts-of-maharashtra-in-5-years-cm-devendra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>'Birthday boy' Fadnavis basks in praise from rivals Uddhav, Pawar; says 'we are not enemies'</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/'birthday-boy'-fadnavis-basks-in-praise-from-rivals-uddhav,-pawar;-says-'we-are-not-enemies'/2751268</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Maharashtra: CM Medical Aid Fund Gets FCRA Nod, Foreign Donations and Crowdfunding to Boost Patient Support</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-cm-medical-aid-fund-gets-fcra-nod-foreign-donations-and-crowdfunding-to-boost-patient-support-a525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Shobha Karandlaje (@ShobhaBJP)</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://x.com/shobhabjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Thank you for the kind birthday wishes, Hon Sarbananda Sonowal ji !</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://x.com/Dev_Fadnavis/status/1947620859717521822</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Thank you for the kind birthday wishes, @kishanreddybjp ji !</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://x.com/Dev_Fadnavis/status/1947621381950292086</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Wishing Shri Devendra Fadnavis ji a very happy birthday. On this occasion, I wish you good health, personal happiness, and well-being. May the coming year bring peace and balance in both your personal and professional life. #DevendraFadnavis #Birthday</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://x.com/hulyalkarshiva/status/1947576184289824968</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Thank you for the kind birthday wishes V. Somanna ji !</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://x.com/Dev_Fadnavis/status/1947628029645361459</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PM Modi &amp; Leaders Extend Birthday Wishes To Maharashtra Chief Minister Devendra Fadnavis &amp; Deputy CM Ajit Pawar https://freepressjournal.in/mumbai/pm-modi-leaders-extend-birthday-wishes-to-maharashtra-chief-minister-devendra-fadnavis-deputy-cm-</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://x.com/fpjindia/status/1947654238093328393</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Heartfelt Birthday Wishes to Shri Devendra Fadnavis Ji, Hon’ble Chief Minister of Maharashtra. Your visionary leadership, unwavering dedication, and commitment to public service continue to inspire countless citizens. On this special day, I pray for your good</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://x.com/BabuKavlekar/status/1947595089397666033</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Heartfelt birthday wishes to Maharashtra’s Hon’ble Chief Minister Shri. Devendra Fadnavis ji and Deputy Chief Minister Shri. Ajitdada Pawar ji! Wishing you both a long and healthy life. @Dev_Fadnavis @AjitPawarSpeaks #DevendraFadnavis #AjitPawar #Ma</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://x.com/AslamShaikh_MLA/status/1947565836161761657</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Birthday wishes to Chief Minister, Maharashtra, Shri Devendra Fadnavis Ji. Wishing you a healthy, happy and long life. @Dev_Fadnavis</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://x.com/ShuklaRajiv/status/1947603495219302517</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Chief minister Devendra Fadnavis urged not to attach political motives to birthday greetings, including those extended by his political rivals.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://x.com/htTweets/status/1948184854472081848</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>My birthday wishes to Maharashtra Chief Minister Shri Devendra Fadnavis avaru. May the almighty grant him good health and a long life. @Dev_Fadnavis</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://x.com/H_D_Devegowda/status/1947576981195001918</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Birthday wishes to Agriman CM Devendra Fadnavis—the one who empowered our farmers with technology, irrigation, and market access. Your impact on rural Maharashtra is inspiring. #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://x.com/KulkarniReyansh/status/1947574522250424426</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Warmest birthday wishes to the Hon’ble Chief Minister of Maharashtra, Shri Devendra Fadnavis Ji. I’ve always admired your unwavering dedication, clarity of purpose, and deep commitment to the people of Maharashtra. Your leadership stands out—not just fo</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://x.com/jaxayshah/status/1947572878846624102</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Wrong to give political colour to birthday wishes of Pawar, Thackeray: CM Fadnavis https://newsdrum.in/national/wrong-to-give-political-colour-to-birthday-wishes-of-pawar-thackeray-cm-fadnavis-9527452… #DevendraFadnavis #Birthday #SharadPawar #Ud</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://x.com/thenewsdrum/status/1947978179572125818</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>'We Are Not Enemies': Maharashtra CM Devendra Fadnavis Thanks Sharad Pawar &amp; Uddhav Thackeray For Birthday Wishes https://freepressjournal.in/mumbai/we-are-not-enemies-maharashtra-cm-devendra-fadnavis-thanks-sharad-pawar-uddhav-thackeray</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://x.com/fpjindia/status/1948022327419302309</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Differently abled students met CM @Dev_Fadnavis and gave him birthday wishes, for which CM Devendra Fadnavis sincerely expressed his heartfelt gratitude. #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://x.com/pb3060/status/1947671154942218616</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Happy Birthday And Warm Birthday Wishes To Maharashtra Chief Minister Shri Devendra Fadnavis🍫🎂 @Dev_Fadnavis #DevendraFadnavis</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://x.com/sachiinv7/status/1947622063038181397</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis has made remarkable strides in rural development, earning heartfelt birthday wishes on his special day. #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://x.com/neeraj__sethii/status/1947558228977717348</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>🌸 Birthday Greetings to Hon’ble CM of Maharashtra, Shri Devendra Fadnavis ji 🌸 Wishing you a very happy birthday Sir ji ! DEVA BHAU of Maharashtra ! May Lord Mahadev bless you with long life, good health, and unbounded strength to continue serving Ma</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://x.com/BajpaiUsha/status/1947739654595481976</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Heartiest Birthday Greetings to the dynamic and popular Chief Minister of Maharashtra Shri Devendra Fadnavis. Wish you a Healthy and Long Life dedicated in serving for a #ViksitMaharashtra and welfare of people. @Dev_Fadnavis #DevendraFadnavis #HB</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://x.com/PrakashJavdekar/status/1947661358297706911</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Warm birthday greetings to CM Devendra Fadnavis—the man who turned bureaucracy into delivery. Your unmatched execution speed has become a benchmark across India. #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://x.com/NehaKulkarn/status/1947625357974376794</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Warm birthday greetings to the Hon’ble Chief Minister of Maharashtra, Shri Devendra Fadnavis Ji.. Wishing you Healthy and Long Life Sir.💐🙏 @Dev_Fadnavis Dr. Ramachandrareddy. BJP State Leader,Andhra Pradesh.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://x.com/rcreddyy/status/1947574695928463462</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sanatan Sanstha extends heartfelt birthday greetings to Shri Devendra Fadnavis (@Dev_Fadnavis), Hon’ble Chief Minister of Maharashtra. May you be blessed by Bhagwan Shri Krishna with divine strength, long life, and continued success in serving Rashtra</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://x.com/SanatanSanstha/status/1947613189874848051</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Hindu Janajagruti Samiti wishes a very Happy birthday to Shri Devendra Fadnavis (@Dev_Fadnavis), Hon’ble Chief Minister of Maharashtra. May Bhagwan Shri Ram grant you strength, good health, and the clarity to lead with righteousness, courage, and unw</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://x.com/HinduJagrutiOrg/status/1947614534329680259</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Nilesh Makwana 🇮🇳🇮🇳 (@N_M12_k) on X</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://x.com/N_M12_k/status/1947718833017655422</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Wishing Shri Devendra Fadnavis Ji, Hon’ble Chief Minister of Maharashtra, a very happy birthday! May you be blessed with good health and continued strength in your tireless service to the nation.</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://x.com/visrane/status/1947625235680989414</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Warm Birthday greetings to Hon’ble Maharashtra Chief Minister Shri Devendra Fadnavis (@Dev_Fadnavis) Ji. Your unwavering dedication to public service and visionary leadership continue to inspire. Praying Mahaprabhu Sri Jagannatha for your good healt</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://x.com/UpasnaMohapatra/status/1947598175608705194</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Heartfelt birthday greetings to Hon’ble Maharashtra Chief Minister Shri Devendra Fadnavis Ji. Your unwavering dedication to public service, visionary leadership, and commitment to Maharashtra’s progress continue to inspire. May you be blessed with abunda</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://x.com/Kompella_MLatha/status/1947591849633583318</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>"संयमी नेतृत्व, दूरदृष्टीचा ध्यास आणि जनतेसाठी झपाटलेला नेता – महाराष्ट्र एकमताने म्हणतो, देवेंद्र फडणवीस म्हणजे यशस्वी नेतृत्वाचा मानबिंदू!" #DevendraFadnavis #MaharashtraCM #HBDDevaBhau #</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://x.com/Devendra4Maha/status/1947874031405044158</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Happy birthday @Dev_Fadnavis ji Wishing you more success in days to come @Devendra_Office</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://x.com/SamirKagalkar/status/1947571563848733113</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Best wishes to Hon. Maharashtra Chief Minister, Shri Devendra Fadnavis Ji on his birthday. @Dev_Fadnavis</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://x.com/AnitaSubhadars1/status/1947552567384498325</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Birthday greetings to the Hon’ble Chief Minister of Maharashtra, Shri Devendra Fadnavis Ji. May he be blessed with good health, a long life, and continued success in his service to the people. @Dev_Fadnavis</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://x.com/DrNiranthar/status/1947570729874296838</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र को नई दिशा देने वाले कर्मयोगी, दूरदर्शी, जनप्रिय नेता श्री देवेंद्र फडणवीस जी @Dev_Fadnavis को जन्मदिन की ढेरों शुभकामनाएँ। ईश्वर आपको उत्तम स्वास्थ्य और दीर्घायु प्रदान करें। 🙏</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://x.com/syed_services/status/1947706854806560893</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>To the dynamic leader—Devendra Fadnavis Ji, wishing you a birthday as monumental as the metro milestones you've achieved. You've laid the tracks for a brighter future!#HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://x.com/iamSureshParmar/status/1947569994910289949</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Warm Birthday greetings to Shri Devendra Fadnavis Ji, Hon’ble Chief Minister of Maharashtra. May you be blessed with good health and energy to continue your dedicated service to the people of Maharashtra and our Nation மகாராஷ்டிர முதலம</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://x.com/bjp_parameswari/status/1947594367536947290</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Wishing a very Happy Birthday to our visionary leader, Hon. Shri Devendra Fadnavis ji! Your dedication, transformative leadership, and commitment to public service continue to inspire Maharashtra and the nation. May you achieve greater milestones in the jo</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://x.com/kunalpadole/status/1947569937603563944</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>To the metro pioneer—Devendra Fadnavis Ji, wishing you a birthday as fast-paced as the metros you've built. Your leadership has accelerated progress and transformed cities! #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://x.com/iParadox/status/1947570219251085516</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Happy birthday @Dev_Fadnavis ! Wish you live a life devoted for the people , which brings about betterment of the people &amp; may you always be showered with lots of love from the people … ! #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://x.com/fadnavis_amruta/status/1947570239979589767</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Warm birthday wishes to Maharashtra’s CM Shri @Dev_Fadnavis ji. Your dedication, leadership, and commitment to public service continue to inspire. Wishing you good health, happiness, and continued success in all your endeavours. #HappyBirthday #Dev</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://x.com/vijayjdarda/status/1947591224770339155</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Happy birthday to Devendra Fadnavis ji, the architect of a Naxal-free and progressive Gadchiroli. Wishing success that never ends, Deva Bhau, you set the trends!.#HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://x.com/Pramod_Mehta1/status/1947596096248873181</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://x.com/goldenarcher/status/1947553145158307842</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Wishing a very Happy Birthday to the Hon’ble Chief Minister of Maharashtra and Chairperson of the Governing Council, VSTF – Shri Devendra Fadnavis ji.</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://x.com/MVSTForg/status/1947634815207149930</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>काल मुख्यमंत्री देवेंद्र फडणवीस यांचा वाढदिवस पार पडला, फडणवीसांच्या वाढदिवसाच्या निमित्ताने अमृता फडणवीस यांनी त्यांच्या सोशल मिडियावर केलेली पोस्ट चांगलीच व्हायरल होते. #Devend</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://x.com/navarashtra/status/1947965760095281238</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Birthday greetings to Hon’ble Maharashtra CM Shri @Dev_Fadnavis Ji. Wishing you good health and strength in your continued service to the state and the nation.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://x.com/Paka4BJP/status/1947567939538063771</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>On CM Devendra Fadnavis' birthday today, a coffee table book titled 'Maharashtra Nayak' was released at the hands of Mah Governor C. P. Radhakrishnan in Mumbai. The idea of the book has been conceived by Min Girish Mahajan. The book contains article</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://x.com/NEWSDAILY123/status/1947609611235909761</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>#DevendraFadnavis ji Birthday Happy Birthday, @Dev_Fadnavis ! Wishing you a year of success and happiness! @Devendra_Office #happybirthdayfadnavis #CM #FadnavisLeadership #bjp #Maharashtra</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://x.com/ihirenjoshi1111/status/1947604156111589535</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Usha Bajpai 🇮🇳 (@BajpaiUsha)</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://x.com/bajpaiusha</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Birthday Greetings to Boss @Dev_Fadnavis Ji. ‘Deva Bhau’ as we Maharashtrians know him, is not just any ordinary leader, he is the Future of Bharat, the perfect intellectual mind, a nation needs, filled with commitment to his roots, vision, ideology &amp; developm</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://x.com/SatyamSurana/status/1947620816146903252</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र राज्याचे मुख्यमंत्री व गृहमंत्री मा.ना.श्री. देवेंद्रजी फडणवीस यांना वाढदिवसाच्या मनःपूर्वक शुभेच्छा. त्यांना उदंड व निरोगी आयुष्य लाभो ही सदिच्छा. @Dev_Fadnavis #nareshmhask</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://x.com/nareshmhaske/status/1947556801853198832</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Wishing a very Happy Birthday to @Dev_Fadnavis Bhau! 🎉 Your leadership, vision, &amp; dedication continue to inspire Maharashtra and beyond. May you always be blessed with strength, success &amp; good health.💪🌟 #HBDDevaBhau #DevendraFadnavis #Leade</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://x.com/IamRinkuThakur/status/1947623466091614650</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>संयमी नेतृत्व, दूरदृष्टीचा ध्यास आणि जनतेसाठी झपाटलेला नेता – महाराष्ट्र एकमताने म्हणतो, देवेंद्र फडणवीस म्हणजे यशस्वी नेतृत्वाचा मानबिंदू..! @Dev_Fadnavis #DevendraFadnavis #MaharashtraCM #</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://x.com/Jaykishan_Hedau/status/1947893317683040583</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Nagpur | On Uddhav Thackeray praising Devendra Fadnavis, Maharashtra Minister Chandrashekhar Bawankule says, "It is a part of Maharashtra's cultural tradition to appreciate and commend the good work and achievements of an individual on their birthday.</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://x.com/ANI/status/1947864832407179291</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>संयमी नेतृत्व, दूरदृष्टीचा ध्यास आणि जनतेसाठी झपाटलेला नेता – महाराष्ट्र एकमताने म्हणतो, देवेंद्र फडणवीस म्हणजे यशस्वी नेतृत्वाचा मानबिंदू..! #DevendraFadnavis #MaharashtraCM #HBDDevaBhau #</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://x.com/kelkaravadhut/status/1947890624599818709</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>#DevendraFadnavis #HBDDevendraFadnavis #BJP4Maharashtra #PragatiPath #VisionaryLeader #MaharashtraDevelopment #SevaSaptah #LokpriyNeta #BirthdayWishes</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://x.com/officeofomsingh/status/1947584031966519602</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ಮಹಾರಾಷ್ಟ್ರದ ಮುಖ್ಯಮಂತ್ರಿಗಳಾದ ಶ್ರೀ @Dev_Fadnavis ಅವರಿಗೆ ಹುಟ್ಟುಹಬ್ಬದ ಹಾರ್ದಿಕ ಶುಭಾಶಯಗಳು.‌ ನಿಮ್ಮ ನಾಯಕತ್ವದಲ್ಲಿ ಮಹಾರಾಷ್ಟ್ರವು ಹೊಸ ಎತ್ತರವನ್ನು ತಲುಪಲಿ. ನಿಮಗೆ ಉತ್ತಮ ಆರೋಗ</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://x.com/b_mattimadu/status/1947577214771376316</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Tajinder Singh Tiwana (@TajinderTiwana)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://x.com/tajindertiwana</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Hon Sir Your birthday celebration was, in every true sense, a reflection of a true People’s Leader — “For the People, By the People, Of the People — and most importantly, With the People.” Happy Birthday #DevendraFadnavis Sir Highest Regards</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://x.com/iamAbhi9/status/1947724878158958729</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Wishing @Dev_Fadnavis ji a very happy birthday. 💐💐 Very few leaders in the country combine vision, empathy &amp; execution like Devendraji and look forward to a Viksit Maharashtra under his leadership..</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://x.com/sudhirmehtapune/status/1947577163148038479</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Vijay Kalantri (@kalantri_vijay)</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://x.com/kalantri_vijay</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Neeraj 🇮🇳 (@neeraj__sethii)</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://x.com/neeraj__sethii</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>🇮🇳 जीवेत शरद: शतम् शतम् 🚩 'उत्तम प्रशासक', जनतेच्या प्रश्नांची जाण असलेला 'संवेदनशील नेता', राज्याच्या विकासाची व्हिजन असलेला 'इन्फ्रामॅन', सिद्ध होणे तर दूर पण भ्रष्टाचाराचा आरोपही नसले</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://x.com/mukund4637/status/1947568736380326205</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Chandrakant Babu Kavlekar (@BabuKavlekar)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://x.com/babukavlekar</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>संयमी नेतृत्व, दूरदृष्टीचा ध्यास आणि जनतेसाठी झपाटलेला नेता – महाराष्ट्र एकमताने म्हणतो, देवेंद्र फडणवीस म्हणजे यशस्वी नेतृत्वाचा मानबिंदू..! #DevendraFadnavis #MaharashtraCM #HBDDevaBhau #</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://x.com/Priiyam/status/1947888747904963048</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Rajesh Chopra (@ichoprarajesh)</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://x.com/ichoprarajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Sending birthday wishes to CM Devendra Fadnavis for schemes like 'Ladli Laxmi' empowering sisters. #HBDDevaBhau.</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://x.com/themanishgarg/status/1947558264155070485</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्रजींच्या वाढदिवसानिमित्त सेवायज्ञ.! राज्याचे लोकप्रिय मुख्यमंत्री मा.देवेंद्र फडणवीस साहेब यांच्या वाढदिवसाचे औचित्य साधून, आज पाटोदा (जि. बीड) उपविभागातील महा</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://x.com/SureshDhasBJP/status/1947668253691809838</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>India Water Foundation (@IndiaWaterFoun1)</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://x.com/indiawaterfoun1</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>संयमी नेतृत्व, दूरदृष्टीचा ध्यास आणि जनतेच्या विकासासाठी सदैव प्रयत्नशील नेता #महाराष्ट्र एकमताने म्हणतो, #देवेंद्र_फडणवीस म्हणजे यशस्वी नेतृत्वाचा मानबिंदू.. #DevendraFadnavis #Maharas</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://x.com/SAMS40308903/status/1947893501988847827</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>S N Channabasappa (Chenni) (@chennibjp)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://x.com/chennibjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Eknath Shinde - एकनाथ शिंदे (@mieknathshinde)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://x.com/mieknathshinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sneha Dube Pandit (@snehadubepandit)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://x.com/snehadubepandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>जनतेच्या मनात घर करून बसणाऱ्या आमच्या देवा काकांना वाढदिवसाच्या खूप खूप शुभेच्छा!🎂💐💐 #DevendraFadnavis #DevendraFadnavis4Maha #devendrafadnavisbirthday #MaharashtraCM #BJP #HBDDevaBhau #BirthdayWishe</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://x.com/KulkarniReyansh/status/1947620129531171090</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>सदैव प्रेरणास्थान… Strong. Visionary. Grounded. Wishing you a cheerful Happy Birthday Devabhau! @Dev_Fadnavis #HBDDevendraFadnavis #DevendraFadnavis #Devabhau #NetaNo1 #leadershipmatters #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://x.com/snehadubepandit/status/1947598682217714064</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>What an inspiring tribute! @joshivikrant75 ji you have beautifully captured CM Devendra Fadnavis' dedication and leadership towards an Unstoppable Maharashtra. DF is A True Legend! 🫡 Proud to have Deva Bhau as our Leader 💯 Everyone should read this</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://x.com/Ayush_Shah_25/status/1947583737807433762</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>धोरणलकव्यातून सक्षम नेतृत्वाकडे नेणाऱ्या कार्यकुशल देवाभाऊंना भारताच्या पंतप्रधान मोदीजींकडून वाढदिवसाच्या सहर्ष शुभेच्छा!💐💐 #NarendraModi #PMModi #DevendraFadnavis #DevendraFadnavis4Mah</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://x.com/KulkarniReyansh/status/1947616737941426500</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>BJP Barabanki(मोदी का परिवार) (@bjp4bbk)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://x.com/bjp4bbk</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Wishing CM of Maharashtra @Dev_Fadnavis, ji a very happy birthday! May the year ahead bring you good health, God bless you #DevendraFadnavis ji D - Dashing E-Energetic V - Versatile E-Effective N - Noble D - Dynamic. R - Reliable A - Admirable.</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://x.com/imransolanki313/status/1947877628876144916</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Wishing you a very Happy Birthday @Dev_Fadnavis May you be blessed with robust health, unwavering strength, and immense success in all your endeavors. As a visionary leader, your dedication to Maharashtra’s progress inspires millions.</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://x.com/ReginaldoGoa/status/1947566450605969642</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Current PM wishing future PM</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://x.com/mydaymywin/status/1947642888981971122</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Raman Suri BJP (@RamanSuriJnk)</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://x.com/ramansurijnk</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Happy Birthday to Hon. CM Shri Devendra Fadnavis Ji. A true visionary whose leadership ignites change. Grateful for the shared moments of inspiration. — Gandhar Group #gandhar #chiefminister #chiefministermaharashtra #devendrafadnavis #india [Gandh</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://x.com/Divyol/status/1947651481349263571</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Mahendra Luhar (@m_luhar)</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://x.com/m_luhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Prabhakar Kore (@prabhakarbkore)</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://x.com/prabhakarbkore</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>BJYM MUMBAI (@BJYM4Mumbai)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://x.com/bjym4mumbai</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Rahul Lonikar (@lonikar_rahul)</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://x.com/lonikar_rahul</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Sharad Pawar : सत्तेत नसतानादेखील बुद्धिचातुर्याच्या बळावर...; पवारांकडून फडणवीसांवर कौतुकाची थाप #sharadpawar #DevendraFadnavis #DevendraFadnavisBirthdayWeek @Dev_Fadnavis @Devendra_Office @BJP4Mahar</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://x.com/mymahanagar/status/1947657093508698193</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Happy birthday @Dev_Fadnavis ! Wish you live a life devoted for the people , which brings about betterment of the people &amp; may you always be showered with lots of love from the people … ! #HBDDevaBhau</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://x.com/fadnavis_amruta/status/1947570239979589767/history</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Sanatan Sanstha (@SanatanSanstha)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://x.com/sanatansanstha</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Janak Patel (Bagdana) (@janak_bagdana)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://x.com/janak_bagdana</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>M𝖆𝖍e𝖘𝖍 Her𝖆𝖒b𝖍𝖆 (@MahiHerambha)</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://x.com/MahiHerambha</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Mahant Daleep Rawat (@MahantDilipRwt)</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://x.com/mahantdiliprwt</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>शतमनाम् भवति शतायुः पुरुषः शतेन्द्रिय आयुष्यएवेन्द्रीये प्रतितिष्ठति || रोचनो रोचमनाः, शोभनाः सोभमानः कल्याणः | Birthday greetings to young, energetic, &amp; suceesful CM of Maharashtra Sri @Dev_Fadnavis ji. Ma</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://x.com/ramapriya1989/status/1947619569092465131</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Central Bureau of Communication, TN &amp; Puducherry (@CBCCHENNAI_MIB)</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://x.com/cbcchennai_mib</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Governor of Maharashtra (@maha_governor)</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://x.com/maha_governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Vishwas Pathak (@vishwasvpathak)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://x.com/vishwasvpathak</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Thank you so much @Dev_Fadnavis ji🙏🙏🙏 It’s your birthday, but you have made my day DevaBhau 🙂🙂🙏🙏</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://x.com/pallavict/status/1947725572295295151</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Thank you so much @Dev_Fadnavis ji🙏🙏🙏 It’s your birthday, but you have made my day DevaBhau 🙂🙂🙏🙏</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://x.com/pallavict/status/1947725572295295151?lang=bg</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Girish Mahajan (@girishdmahajan)</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://x.com/girishdmahajan</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Naresh Mhaske (@nareshmhaske)</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://x.com/nareshmhaske</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>आमच्या लाडक्या मुख्यमंत्री @Dev_Fadnavis देवा भाऊंवर दाखवलेल्या विश्वासा बद्दल.. आणि त्यांना त्यांच्या वाढदिवसानिमित्त दिलेल्या शुभेच्छां साठी.. आम्ही समस्त मराठी प्रांतीय आभार</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://x.com/rrrrajput/status/1947554753522856259</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Dr. C.N. Ashwath Narayan (@drashwathcn)</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://x.com/drashwathcn</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Dr. Ashishrao R. Deshmukh (@AshishRDeshmukh)</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://x.com/ashishrdeshmukh</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Mrityunjay Bose (@MBTheGuide)</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://x.com/mbtheguide</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Prabhakar Acharya 🇮🇳 🚩 (@Prabhak41657341)</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://x.com/prabhak41657341</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Anitha Vangalapudi (@Anitha_TDP)</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://x.com/anitha_tdp</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>VIDEO : उद्धव ठाकरेंकडून देवेंद्र फडणवीसांचं कौतुक, नेमकं काय म्हणाले बघा? https://tv9marathi.com/videos/uddhav-thackeray-praises-and-birthday-wishes-maharashtra-cm-devendra-fadnavis-1452042.html… #UddhavThackeray #dev</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://x.com/TV9Marathi/status/1947624287764156910</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Tushar Hinge (मा. उपमहापौर, पिंपरी-चिंचवड) (@TusharRHinge)</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://x.com/tusharrhinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Ajay Tamta (@AjayTamtaBJP)</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://x.com/ajaytamtabjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Astrologer Dr Prem Sharma (@premastrologer)</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://x.com/premastrologer</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Phalguni Patra (@PhalguniPatraWB)</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://x.com/phalgunipatrawb</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Biplab Kumar Deb (@BjpBiplab)</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://x.com/bjpbiplab</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Pradipsinh Jadeja (@PradipsinhGuj)</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://x.com/pradipsinhguj</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Rahul Rathod (@RVRathod700)</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://x.com/rvrathod700</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Nityanand Rai (@nityanandraibjp)</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://x.com/nityanandraibjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Dr.RamaChandraReddy Yeluri ( Modi ka Parivar ) (@rcreddyy)</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://x.com/rcreddyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>"मैं कामना करती हूँ कि आप लोगों के लिए समर्पित जीवन जिएँ, जिससे लोगों की भलाई हो और आपको लोगों का ढेर सारा प्यार हमेशा मिलता रहे..." अमृता फडणवीस ने अपने पति और महाराष्ट्र के CM देवेंद्र फ</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://x.com/TheNavbharatliv/status/1947626329475530765</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>George Kurian (@GeorgekurianBjp)</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://x.com/georgekurianbjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Dushyant Kumar Gautam (@dushyanttgautam)</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://x.com/dushyanttgautam</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Rajesh P. Sharma (@RajeshSharmaINC)</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://x.com/rajeshsharmainc</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Gauri shankar Verma (MLA) (Modi ka Parivar) (@GsvermaB)</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://x.com/gsvermab</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Sandip Desai Bjp (@MLASandipDesai)</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://x.com/mlasandipdesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>G Kishan Reddy (@kishanreddybjp)</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://x.com/kishanreddybjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Praveen Khandelwal (@PKhandelwal_MP)</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://x.com/pkhandelwal_mp</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Dr. Sanjay Jaiswal (Modi Ka Parivar) (@sanjayjaiswalMP)</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://x.com/sanjayjaiswalmp</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Santosh Danve (@SantoshDanveBJP)</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://x.com/santoshdanvebjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Right Singh (@rightwingchora)</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://x.com/rightwingchora</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Kausar Jahan (@Kausarjahan213)</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://x.com/kausarjahan213</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Satyendra Nagar (@SatyendraNagar8)</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://x.com/satyendranagar8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Rais Shaikh (@rais_shk)</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://x.com/rais_shk</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>देशाच्या नेतृत्वाकडून महाराष्ट्राच्या नेतृत्वाला वाढदिवसाच्या शुभेच्छा #DevendraFadnavis #MaharashtraCM #NarendraModi #HBDDevaBhau #devendrafadnavisbirthday #BJP</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://x.com/Devendra4Maha/status/1947563818651160727</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>RITOJ🇮🇳 (@im_Ritoj)</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://x.com/im_ritoj</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Sanjoy Kishan (@sanjoykishan1)</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://x.com/sanjoykishan1</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Raju Bista (@RajuBistaBJP)</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://x.com/rajubistabjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>S. Rajiv Krishna (@RajivKrishnaS)</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://x.com/rajivkrishnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>ಅಶೋಕ ಕೆ (@kumarak2101)</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://x.com/kumarak2101</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Upasna Mohapatra (@UpasnaMohapatra)</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://x.com/upasnamohapatra</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Nitesh Rane (@NiteshNRane)</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://x.com/niteshnrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>In 2014, @Dev_Fadnavis started the CM Relief Fund helpdesk to support poor and needy patients. Since then, over ₹1500 crore has been given to save lives and bring hope to thousands of families. This is not just politics - this is seva in true sense. Wishing a</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://x.com/ag_arpit1/status/1947595974827712829</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Posts with replies by Astrologer Dr Prem Sharma (@premastrologer)</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://x.com/premastrologer/with_replies</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Sunil Deodhar (@Sunil_Deodhar)</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://x.com/sunil_deodhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Avadhut Kelkar (@kelkaravadhut)</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://x.com/kelkaravadhut</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Neel Shah 🇮🇳 #BJP (@neelshah31790)</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://x.com/neelshah31790</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Team Devendra (@Team__Devendra)</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://x.com/team__devendra</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Sai Kiran Akula 🟦 (@_an__indian)</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://x.com/_an__indian</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>देवेंद्रांच्या कार्याची गती अफाट, ते थकत कसे नाहीत, हा प्रश्न मला पडतो; शरद पवारांकडून फडणवीसांवर कौतुकाचा वर्षाव https://marathi.abplive.com/news/politics/sharad-pawar-praises-cm-devendra-fadnavis-work-style-an</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://x.com/abpmajhatv/status/1947594643019075848</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Rajani Patil (@rajanipatil_in)</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://x.com/rajanipatil_in</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Shrikant Sharma (@ptshrikant)</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://x.com/ptshrikant</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>SagaR Tyagi (@SagarTyagiBJP)</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://x.com/sagartyagibjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Hemant Rasane (@HemantNRasane)</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://x.com/hemantnrasane</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Mangal Prabhat Lodha (@MPLodha)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://x.com/mplodha</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Ashok Chavan (@AshokChavan1958)</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://x.com/ashokchavan1958</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Amita Sachdeva, Advocate (@SachdevaAmita)</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://x.com/sachdevaamita</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Prashant Thakur (@ithakurprashant)</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://x.com/ithakurprashant</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Bharat Sanghvi Jain (@rajamaka)</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://x.com/rajamaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Malkit Bal (@BalMalkitSingh)</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://x.com/balmalkitsingh</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Adv.Priyanka Dubey (Pihu) 🇮🇳 (@AdvPriyankaBJP)</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://x.com/advpriyankabjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>#HBDDevaBhau #Maharashtra</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://x.com/girish_joshig/status/1947684922627666360</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Sanjay Gaikwad - संजय गायकवाड (@sanjaygaikwad34)</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://x.com/sanjaygaikwad34</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Pravin Darekar - प्रविण दरेकर (@mipravindarekar)</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://x.com/mipravindarekar</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>महाराष्ट्राचे लाडके मुख्यमंत्री ‘देवा भाऊ’ ~ मा. श्री. @Dev_Fadnavis जी यांना वाढदिवसाच्या मनःपूर्वक शुभेच्छा! सामान्य माणसाच्या जीवनात ठोस बदल घडवण्यासाठी तुमची असलेली कामाची तळमळ</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://x.com/MurjiPatel_/status/1947592519119966247</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Dr. Bharati Lavekar (@LavekarBharati)</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://x.com/lavekarbharati</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Adv. Santosh Pandey (Modi Ka Parivar) (@SantoshPandeBJP)</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://x.com/santoshpandebjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Dr. Parinay Fuke (@Parinayfuke)</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://x.com/parinayfuke</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Vikrant Balasaheb Patil (@ivikrantpatil)</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://x.com/ivikrantpatil</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Chitra Kishor Wagh (@ChitraKWagh)</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://x.com/chitrakwagh</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Raksha Khadse (@khadseraksha)</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://x.com/khadseraksha</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Radhakrishna Vikhe Patil (@RVikhePatil)</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://x.com/rvikhepatil</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Manisha Chaudhary (@manishaBJP)</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://x.com/manishabjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Yogesh Tilekar (@iYogeshTilekar)</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://x.com/iyogeshtilekar</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Parag Shah (@ParagShahBJP)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://x.com/paragshahbjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Ameet Satam (@AmeetSatam)</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://x.com/ameetsatam</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Zahid Yunus Khan (@AapkaZahidKhan)</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://x.com/aapkazahidkhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Honest, Common Citizen of India Vinita Deshmukh (@VinitaDeshmukh)</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://x.com/vinitadeshmukh</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Anitha Chandra 🇮🇳 (@Anitha_Chandraa)</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://x.com/anitha_chandraa</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Ramdas Tadas (@RamdasTadasMP)</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://x.com/ramdastadasmp</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Mangesh Chavan (@mlamangeshbjp)</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://x.com/mlamangeshbjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>आ. अमोल गोदावरी रामकृष्ण मिटकरी (@amolmitkari22)</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://x.com/amolmitkari22</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>amol balwadkar (@BalwadkarAmol)</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://x.com/balwadkaramol</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Akash Fundkar (@advakash)</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://x.com/advakash</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Aleixo Reginaldo Lourenco (@ReginaldoGoa) on X</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://x.com/reginaldogoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Chhagan Bhujbal (@ChhaganCBhujbal)</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://x.com/chhagancbhujbal</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Mukesh Tiwari (@_Mukesh_Tiwari6)</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://x.com/_mukesh_tiwari6?lang=ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Lahu Balwadkar (@LBalwadkar)</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://x.com/lbalwadkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Gautam Kamble (@Gautam88Kamble)</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://x.com/Gautam88Kamble</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>KALURAM BARNE (@ikalurambarne)</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://x.com/ikalurambarne</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Kishor bhanudas shinde (@KishorShinde984)</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://x.com/kishorshinde984</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Posts with replies by Onkar Dake (@OnkarDake225)</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://x.com/OnkarDake225/with_replies</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Mota Bhai - The Proud Hindu (@THEHINDUTRUMP)</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://x.com/thehindutrump</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Vaishali chopde ( मोदी का परिवार) (@drvaishali1308)</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://x.com/drvaishali1308</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>समीर चाकू (गौरवान्वित सनातनी) (@chakusameer)</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://x.com/chakusameer</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Mukesh Tiwari (@_Mukesh_Tiwari6)</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://x.com/_Mukesh_Tiwari6</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Dipesh Dharankar (@DharankarDipesh)</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://x.com/DharankarDipesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Why does govt. work only for the so-called poor and downtrodden? When will it work for normal humans? When will infrastructure improve ? When will reservations end? When will the atrocity act be cancelled ? When will anti-male laws be nullified? When will</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://x.com/PoojaPophale/status/1947648509928194404</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>जनतेच्या मनात घर करणाऱ्या देवाभाऊंच्या कार्याला सलाम आणि वाढदिवसाच्या शुभेच्छा...♥️🎂 #NarendraModi #DevendraFadnavis #DevendraFadnavis4Maha #DevendraFadnavisBirthdayWeek #HappyBirthdayDevendraFadn</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://x.com/mazi_shivsainik/status/1947586918864003179</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Poongodi Suganth (Modi Ka Parivar) (@PoongodiSugandh)</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://x.com/poongodisugandh</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Manoj K (@Manojlucky2)</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://x.com/Manojlucky2</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Rakesh Asati 🇮🇳 (@RakeshAsati5)</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://x.com/rakeshasati5</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>भविष्यात #प्रधानसेवक म्हणून आपण या भारत देशाला सुजलाम सुफलाम करावे हीच परमेश्र्वराकडे प्रार्थना. पुनश्च एकदा वाढदिवसाच्या मनःपूर्वक शुभेच्छा व खूप सारे प्रेम!❤️💐 #DevendraFadnavis #devabh</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://x.com/Niranjan3112/status/1947760482619637761</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Apparaju Janardhana Rao Sharma ji (@JanardhanaJi)</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://x.com/janardhanaji</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Yogendra Singh Bhati (@yogendra4Bwr)</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://x.com/yogendra4Bwr</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Sam B (@samspeaks19)</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://x.com/samspeaks19</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>MLA Rais Shaikh Fan Club (@RiseWithRais)</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://x.com/risewithrais</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Tejas amrutkar (@tejasamrutkar75)</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://x.com/tejasamrutkar75</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Kiran Bhor (@bhokirani)</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://x.com/bhokirani</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Tokugawa Iyeyasu (@mydaymywin)</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://x.com/mydaymywin</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Reha (@chatterreha)</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://x.com/chatterreha</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>देशाच्या नेतृत्वाकडून महाराष्ट्राच्या नेतृत्वाला वाढदिवसाच्या शुभेच्छा💐🎂 #NarendraModi #PMModi #DevendraFadnavis #DevendraFadnavis4Maha #DevendraFadnavisBirthdayWeek #HappyBirthdayDevendraFadnavis #</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://x.com/DubheRohit/status/1947614135874949590</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Karan ( Modi Ka Parivar ) (@KaranChougule01)</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://x.com/karanchougule01</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>देवेंद्रजी फडणवीस म्हणजे लोकशाहीतील आश्वासक आवाज! संघर्षातून घडलेलं नेतृत्व महाराष्ट्रासाठी अमूल्य आहे. सर, वाढदिवसाच्या हार्दिक शुभेच्छा! #DevendraFadnavis #DevendraFadnavis4Maha #devend</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://x.com/KulkarniReyansh/status/1947610478634799582</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Harish Singh (@harish69665)</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://x.com/harish69665</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>SRINIVASA REDDY YOUTH (@Prasadleela666)</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://x.com/prasadleela666</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>प्रणोती 🇮🇳🇮🇳 (@maibharatwasi)</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://x.com/maibharatwasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>PK Suresh (@pksureshbalagok)</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://x.com/pksureshbalagok</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र राज्याचे मुख्यमंत्री श्री.देवेंद्र फडणवीस यांना वाढदिवसाच्या हार्दिक शुभेच्छा. #DevendraFadnavis #Birthday #Greetings @Dev_Fadnavis</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://x.com/manishp62615211/status/1947871008268161202</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Rathindra Bose (Modi Ka Parivar) (@rathindraOFC)</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://x.com/rathindraofc</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Posts with replies by Adarsh (@Adarsh18795)</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://x.com/Adarsh18795/with_replies</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>अखंड भारत🐦 (@Hindavidragon12)</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://x.com/hindavidragon12</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Madeira (@Madeira7i)</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://x.com/madeira7i</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Teju Kadam (@TejuKadam587975)</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://x.com/TejuKadam587975</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>@fromthekids</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/FromTheKids?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Manoj jha (@md28021992)</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://x.com/md28021992</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>#Devendrafadnavis #devendrafadnaviswishes #investment #hospital #CBSCSchool #township</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/devendrafadnaviswishes?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>InfrastructureLeader</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/InfrastructureLeader?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>#ajitpawarsaheb #NCP</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/AjitPawarSaheb?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>#HBDDevBhau #TeamDevendra</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/HBDDevBhau?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>@Yogeshtilekar</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/yogeshtilekar?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>@Dev_Fadnavis महाराष्ट्र राज्याचे मुख्यमंत्री श्री.देवेंद्र फडणवीस यांना वाढदिवसाच्या हार्दिक शुभेच्छा. #DevendraFadnavis #Birthday #Greetings @Dev_Fadnavis</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://x.com/DuwaYaad/status/1947616642244165741</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>आम्ही इंग्रजीला पायघड्या घालणार नाही’ म्हणणाऱ्या फडणवीसांना इंग्रजीतच वाढदिवसाच्या शुभेच्छा! 😆</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://x.com/samspeaks19/status/1947766969383756249</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Birthday greetings to our Swayamsevak,CM of Maharashtra Shri Devendra Fadnavis ji. My Prayers and good wishes for his good health n long life . May Shiva bless him to serve d people of Maharashtra with war fighting efforts to make our Maha-Rashtra gr8 a</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://x.com/Drek007/status/1947599500748722539</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>MahaRaktdanSankalp</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/MahaRaktdanSankalp?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>hbdd</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/hbdd?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>#CMDevendraFadnavis #JansurakshaVidheyak</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/cmdevendrafadnavis?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>#MinorToolkit So many people deeply concerned about the VP. Even lousy Communists?</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/MinorToolkit?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>जनतेचाआधार</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/%E0%A4%9C%E0%A4%A8%E0%A4%A4%E0%A5%87%E0%A4%9A%E0%A4%BE%E0%A4%86%E0%A4%A7%E0%A4%BE%E0%A4%B0?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>NetaNo1</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/NetaNo1?src=hashtag_click</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Mando (@mando10905)</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://x.com/mando10905</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Bhargavi Iyer (@BhargaviIyer2)</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://x.com/bhargaviiyer2</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>#happybirthdayfadnavis #CM #FadnavisLeadership #bjp #Maharashtra</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/happybirthdayfadnavis?src=hashtag_click&amp;f=live</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Monali C. Rahalkar (@MonaRahalkar)</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://x.com/monarahalkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>#लोकमान्यबाळगंगाधरटिळक #LokmanyaBalGangadharTilak</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/%E0%A4%B2%E0%A5%8B%E0%A4%95%E0%A4%AE%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%AC%E0%A4%BE%E0%A4%B3%E0%A4%97%E0%A4%82%E0%A4%97%E0%A4%BE%E0%A4%A7%E0%A4%B0%E0%A4%9F%E0%A4%BF%E0%A4%B3%E0%A4%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>#MinorToolkit So many people deeply concerned about the VP. Even lousy Communists?</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://x.com/seshanm/status/1947669737942749657</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Nghiêm Thị Mai Ngọc (@mai_thi32430)</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://x.com/mai_thi32430</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>मुंबईचा राजा रोहित शर्मा (@IcaMumba3374)</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://x.com/IcaMumba3374</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Wishing a very Happy Birthday to Hon. Shri Devendra Fadnavis Ji! May you be blessed with good health, long life, and the strength to continue your impactful leadership for Maharashtra. @fadnavis_amruta @Dev_Fadnavis @AmrutaF_fans #HappyBirthday #</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://x.com/DsouzaDaks65109/status/1947568953611718722</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Bành Minh Thủy (@Chudai_Jav_6aVr)</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://x.com/Chudai_Jav_6aVr</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Vũ Duyên My (@duyen_my84780)</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://x.com/duyen_my84780</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>मोहित विश्वकर्मा (@mohitvishwa02)</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://x.com/mohitvishwa02</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>संयमी नेतृत्व, दूरदृष्टीचा ध्यास आणि जनतेसाठी सदैव कार्यरत असलेला नेता – महाराष्ट्र एकमताने म्हणतो, देवेंद्र फडणवीस म्हणजे यशस्वी नेतृत्वाचा मानबिंदू..! #DevendraFadnavis #MaharashtraCM #HB</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://x.com/SuneelBarke2818/status/1947890150555750895</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Diana Mouses (@TuanUc80093)</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://x.com/TuanUc80093</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Nguyễn Yến Hồng (@NguynYnHng77750)</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://x.com/NguynYnHng77750</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Sunil Tetwar (@TetwarSunil)</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://x.com/TetwarSunil</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Oralie Blaine (@ly_nguyet91654)</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://x.com/ly_nguyet91654</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Eminent Intellectual (@totalwoke2)</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://x.com/totalwoke2</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>abhijaanu (@abhivirat09)</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://x.com/abhivirat09</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Edana Artur (@LmKimThanh73511)</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://x.com/LmKimThanh73511</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>ಗೌಡ್ರ ಕಟ್ಟೆ (@IamMMGoudar)</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://x.com/IamMMGoudar</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Lynne Fionah (@Chudai_jav_0NI)</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://x.com/Chudai_jav_0NI</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Junaid Siddiqui (@JunaidS64225266)</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://x.com/JunaidS64225266</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Thái Minh Tiến (@Chudai_Jav_snl2)</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://x.com/Chudai_Jav_snl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Rosaleen Karlee (@inh_ma22648)</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://x.com/inh_ma22648</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Griselda Heather (@LinhNgo45005)</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://x.com/LinhNgo45005</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Iphigenia Sethe (@Chudai_jav_nqJ8)</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://x.com/Chudai_jav_nqJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Arian Azealia (@gia_hiep52511)</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://x.com/gia_hiep52511</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Elfreda Zila (@NhuTran5476)</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://x.com/NhuTran5476</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Suneel Barke (@SuneelBarke2818)</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://x.com/SuneelBarke2818</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Dr. Anil Bonde (@DoctorAnilBonde)</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://x.com/doctoranilbonde</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis says birthday wishes from opposition leaders shouldn’t be politicised</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/cm-devendra-fadnavis-says-birthday-wishes-from-opposition-leaders-shouldnt-be-politicised-23586123</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis responds to birthday praise from Sharad Pawar, Uddhav Thackeray: 'We are not enemies'</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/maharashtra/devendra-fadnavis-55th-birthday-responds-to-praise-from-sharad-pawar-uddhav-thackeray-says-we-are-not-enemies-2025-07-22-1000099</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>'How Does He Not Get Tired': Sharad Pawar Praises Fadnavis In Book Released On CM's Birthday</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/politics/how-does-he-not-get-tired-sharad-pawar-praises-fadnavis-in-book-released-on-cms-birthday-ws-l-9455999.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>PM Modi extends birthday wishes to Fadnavis and Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/pm-modi-extends-birthday-wishes-to-fadnavis-and-ajit-pawar/2750341</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>‘Remarkable…’: Sharad Pawar Praises Maharashtra CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://www.republicworld.com/india/remarkable-sharad-pawar-praises-maharashtra-cm-devendra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>'One cannot deny…': Sharad Pawar's birthday praise for Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/sharad-pawars-birthday-praise-for-devendra-fadnavis-maharashtra-nayak-coffee-book-one-cannot-deny-101753198260918.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>"Part of Maharashtra's tradition", Chandrashekhar Bawankule responds to Uddhav Thackeray's praise for CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Sharad Pawar praises Devendra Fadnavis on his birthday: 'How does he never get tired?'</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/maharashtra/sharad-pawar-praises-maharashtra-chief-minister-devendra-fadnavis-on-his-birthday-wonders-how-does-he-never-get-tired-2025-07-22-1000030</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>PM Modi Extends Birthday Wishes To Devendra Fadnavis, Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/pm-modi-extends-birthday-wishes-to-devendra-fadnavis-ajit-pawar-9455167.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Adityanath greets Fadnavis on birthday</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/Adityanath-greets-Fadnavis-on-birthday/2748482</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>We Are Not Enemies: Maharashtra CM Devendra Fadnavis Thanks Sharad Pawar &amp; Uddhav Thackeray For Birthday</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/we-are-not-enemies-maharashtra-cm-devendra-fadnavis-thanks-sharad-pawar-uddhav-thackeray-for-birthday-wishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis Ajit Pawar Birthday Special News: हॅपी बर्थडेची अशीही एक कहाणी...! N18V</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-ajit-pawar-birthday-special-news-%E0%A4%B9%E0%A5%85%E0%A4%AA-%E0%A4%AC%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A4%A1%E0%A5%87%E0%A4%9A-%E0%A4%85%E0%A4%B6-%E0%A4%B9-%E0%A4%8F%E0%A4%95-%E0%A4%95%E0%A4%B9-%E0%A4%A3-n18v/vi-AA1J5l3Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>CM thanks Sharad Pawar &amp; Uddhav for birthday wishes</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/cm-thanks-sharad-pawar-uddhav-for-birthday-wishes/articleshow/122844648.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>PM Modi, HM Amit Shah Extend Birthday Wishes To Maharashtra Deputy CM Ajit Pawar On His 66th Birthday</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/pm-modi-hm-amit-shah-extend-birthday-wishes-to-maharashtra-deputy-cm-ajit-pawar-on-his-66th-birthday</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Blood drive breaks two world records</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/blood-drive-breaks-two-world-records/articleshow/122866439.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Maha Governor unveils Coffee Table Book on CM Fadnavis, hails his visionary leadership</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/07/22/maha-governor-unveils-coffee-table-book-on-cm-fadnavis-hails-his-visionary-leadership/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>VIDEO: Devendra Fadnavis Most Helpless CM In Maharashtras History, Says Congress Leader Harshwardhan Sapkal</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/video-devendra-fadnavis-most-helpless-cm-in-maharashtras-history-says-congress-leader-harshwardhan-sapkal</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Mumbai-Ahmedabad bullet train project to be fully completed by 2029: Union Railway Minister Vaishnaw</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/cm-devendra-fadnavis-says-birthday-wishes-from-opposition-leaders-shouldnt-be-politicised-23586155</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Navi Mumbai: Woman’s Viral Video Of Aura Farming Dance On Moving Mercedes Car Raises Safety Concerns</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/navi-mumbai-womans-viral-video-of-aura-farming-dance-on-moving-mercedes-car-raises-safety-concerns</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis Full Speech : गडचिरोलीतून फडणवीसांची मोठी घोषणा : Maharashtra Politics</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://lokmat.news18.com/videos/video/cm-devendra-fadnavis-full-speech-fadnavis-s-big-announcement-from-gadchiroli-maharashtra-politics-1066892.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Devendra Fadanvis Birthday: फडणवीस थकत कसे नाहीत? राष्ट्रीय पातळीवर मोठी जबाबदारी मिळेल! शरद पवार आणि उद्धव ठाकरे यांच्याकडून स्तुतिसुमने|VIDEO</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/maharashtra/devendra-fadnavis-birthday-sharad-pawar-uddhav-thackeray-praise-national-leader-potential-om0906</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीसांचं शरद पवारांनी केलं कौतुक, रावसाहेब दानवे म्हणाले, कौतुक करण्यात गैर नाही</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/jalna/sharad-pawar-praises-cm-devendra-fadnavis-on-his-birthday-bjp-leader-raosaheb-danve-reaction-on-this/videoshow/122839819.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Manikrao Kokate: व्हायरल व्हिडीओवर माणिकराव कोकाटेंचे स्पष्टीकरण; म्हणाले…</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5246127/manikrao-kokate-gave-a-explanation-on-the-vidhanbhavan-viral-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Sanjay Raut on Jagdeep Dhankhar: जगदीप धनखड यांच्या राजीनाम्यावर संजय राऊतांचं सूचक विधान</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5246122/sanjay-rauts-suggestive-statement-on-jagdeep-dhankhars-resignation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>India News | PM Modi Extends Birthday Wishes to Fadnavis and Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/india-news-pm-modi-extends-birthday-wishes-to-fadnavis-and-ajit-pawar-7013986.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>PM Narendra Modi Embarks on 2-Nation Visit to UK and Maldives, Hopes Solidify Bilateral Relations (Watch Videos)</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/news/pm-narendra-modi-embarks-on-2-nation-visit-to-uk-and-maldives-hopes-solidify-bilateral-relations-watch-videos-7015715.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Manikrao Kokate Online Rummy Video Controversy: Maharashtra Agriculture Minister Seeks Probe, Says Will</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/politics/manikrao-kokate-online-rummy-video-controversy-maharashtra-agriculture-minister-seeks-probe-says-will-resign-if-found-guilty-7013234.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>India News | We Are Ideological Opponents Not Enemies: Fadnavis on Thackeray, Pawar</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/india-news-we-are-ideological-opponents-not-enemies-fadnavis-on-thackeray-pawar-7014052.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>PM Narendra Modi to Embark on 2-Nation Tour of UK, Maldives Today; Check All Details Here</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/news/pm-narendra-modi-to-embark-on-2-nation-tour-of-uk-maldives-today-check-all-details-here-7014896.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Disturbing Video Shows Adult Actor Dancing Naked While Covered In Blood Of Couple He Killed Moments Before</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/viral/disturbing-video-shows-adult-actor-dancing-naked-while-covered-in-blood-of-couple-he-killed-moments-before</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>PM Modi UK Visit: Prime Minister Narendra Modi Departs for United Kingdom, FTA Signing, Defence and Action</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/pm-modi-uk-visit-prime-minister-narendra-modi-departs-for-united-kingdom-fta-signing-defence-and-action-against-khalistani-extremists-on-agenda-7015684.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Nagpur Airport Bomb Threat: Authorities Say Nothing Suspicious Found During Search Operation After Airport</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/news/nagpur-airport-bomb-threat-authorities-say-nothing-suspicious-found-during-search-operation-after-airport-receives-threatening-mail-7013341.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Narendra Modi Government Has ‘Consistent Policy of Betrayal’ for Jammu and Kashmir, Alleges Congress</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/narendra-modi-government-has-consistent-policy-of-betrayal-for-jammu-and-kashmir-alleges-congress-leader-mallikarjun-kharge-7014767.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>PM Narendra Modi Wishes Jagdeep Dhankhar Good Health After His Sudden Resignation As Vice President of</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/news/pm-narendra-modi-wishes-jagdeep-dhankhar-good-health-says-he-got-many-opportunities-to-serve-country-in-various-capacities-7012968.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>"Ours is a battle of ideas, not personal enmity," says BJP MLA Ram Kadam on Uddhav's praise for Maharashtra CM</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://thenewsmill.com/2025/07/ours-is-a-battle-of-ideas-not-personal-enmity-says-bjp-mla-ram-kadam-on-uddhavs-praise-for-maharashtra-cm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Neeta Mahesh Baldi joins blood donors for CM’s b’day camp</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://www.newsband.in/article_detail/neeta-mahesh-baldi-joins-blood-donors-for-cms-bday-camp</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Part Of Maharashtras Tradition, Minister Chandrashekhar Bawankule Responds To Shiv Sena (UBT) Chief Uddhav</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/part-of-maharashtras-tradition-minister-chandrashekhar-bawankule-responds-to-shiv-sena-ubt-chief-uddhav-thackerays-praise-for-cm-devendra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Massive blood donation camp in Bhusawal</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://www.khabar24.tv/2025/07/23/massive-blood-donation-camp-in-bhusawal-on-the-occasion-of-chief-minister-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>सांसद रक्तदान अभियान के तहत हिवरखेड में हुआ रक्तदान शिविर</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/blood-donation-camp-organized-in-hiwarkhed-under-mp-blood-donation-campaign/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>PM Modi extends birthday wishes to Fadnavis and Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/pm-modi-extends-birthday-wishes-to-fadnavis-and-ajit-pawar/2698643/</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>PM Modi extends birthday wishes to Fadnavis and Ajit Pawar</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/pm-modi-extends-birthday-wishes-to-fadnavis-and-ajit-pawar/2750341</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Viksit Maharashtra 2047: PWD Minister Bhosale Reviews 150-Day Action Plan, Calls For Timely Reforms And Vision</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/viksit-maharashtra-2047-pwd-minister-bhosale-reviews-150-day-action-plan-calls-for-timely-reforms-and-vision-document</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>22.07.2025: Governor Releases Coffee Table Book on CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://rajbhavan-maharashtra.gov.in/en/22-07-2025-governor-releases-coffee-table-book-on-cm-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis curbs funds for developmental projects amid misuse allegations</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/devendra-fadnavis-curbs-funds-for-developmental-projects-amid-misuse-allegations/ar-AA1J8nmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Sewage Projects in 16 Merged Pune Villages Get Rs 533 Cr Boost Under AMRUT 2.0</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/sewage-projects-in-16-merged-pune-villages-get-rs-533-cr-boost-under-amrut-2-0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Mumbai News: Fight To Save Lokhandwala Mangroves Intensifies, Minister Pankaja Munde Orders Probe And</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-fight-to-save-lokhandwala-mangroves-intensifies-minister-pankaja-munde-orders-probe-and-restoration</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Wrong to give political colour to birthday wishes of Pawar, Thackeray: CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/Wrong-to-give-political-colour-to-birthday-wishes-of-Pawar--Thackeray--CM-Fadnavis/2752867</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Grand tree plantation program at RET species botanical garden</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/grand-tree-plantation-program-at-ret-species-botanical-garden/articleshow/122844675.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>No PoP, Only Clay Idols Of Deities To Be Sold In Indore</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/indore/no-pop-only-clay-idols-of-deities-to-be-sold-in-indore</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Maha Governor unveils Coffee Table Book on CM Fadnavis, hails his visionary leadership</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://www.sakshipost.com/news/maha-governor-unveils-coffee-table-book-cm-fadnavis-hails-his-visionary-leadership-431829</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Planting of 3 lakh trees to develop natural habitat at Zoological Park begins</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/aurangabad/planting-of-3-lakh-trees-to-develop-natural-habitat-at-zoological-park-begins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Schools Represent Largest single Philanthropic Contribution To IIT Indore</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/indore/schools-represent-largest-single-philanthropic-contribution-to-iit-indore</t>
         </is>
       </c>
     </row>
